--- a/data/AKHAN (TRY).xlsx
+++ b/data/AKHAN (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>241265518</v>
+        <v>623127053</v>
       </c>
       <c r="C3">
-        <v>252714084</v>
+        <v>258186437.38594788</v>
       </c>
       <c r="D3">
-        <v>197819273.9937931</v>
+        <v>270439645</v>
       </c>
       <c r="E3">
-        <v>73389268.68138549</v>
+        <v>211693133.863962</v>
       </c>
       <c r="F3">
-        <v>1035076135.8672377</v>
+        <v>78536352.72988757</v>
       </c>
       <c r="G3">
-        <v>184741624.0421416</v>
+        <v>1107670180.7954812</v>
+      </c>
+      <c r="H3">
+        <v>197698295.81836355</v>
       </c>
     </row>
     <row r="4">
@@ -474,14 +481,14 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
-      <c r="B5">
-        <v>10379297</v>
-      </c>
-      <c r="D5">
-        <v>374942.4779016518</v>
-      </c>
-      <c r="G5">
-        <v>124767239.76599689</v>
+      <c r="C5">
+        <v>11107238.768370774</v>
+      </c>
+      <c r="E5">
+        <v>401238.69915835623</v>
+      </c>
+      <c r="H5">
+        <v>133517667.19378898</v>
       </c>
     </row>
     <row r="6">
@@ -494,22 +501,25 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>1228248817</v>
+        <v>1112816240</v>
       </c>
       <c r="C7">
-        <v>1160478373</v>
+        <v>1314390837.5863934</v>
       </c>
       <c r="D7">
-        <v>1136779299.649105</v>
+        <v>1241875226</v>
       </c>
       <c r="E7">
-        <v>1638001539.258635</v>
+        <v>1216506195.7610343</v>
       </c>
       <c r="F7">
-        <v>464591039.9432648</v>
+        <v>1752881163.2911663</v>
       </c>
       <c r="G7">
-        <v>1457651374.7867856</v>
+        <v>497174674.76800454</v>
+      </c>
+      <c r="H7">
+        <v>1559882317.733151</v>
       </c>
     </row>
     <row r="8">
@@ -527,22 +537,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>26124262</v>
+        <v>25886301</v>
       </c>
       <c r="C10">
-        <v>29260498</v>
+        <v>27956461.37512737</v>
       </c>
       <c r="D10">
-        <v>97458202.77072482</v>
+        <v>31312852</v>
       </c>
       <c r="E10">
-        <v>103717896.03518628</v>
+        <v>104293337.79645526</v>
       </c>
       <c r="F10">
-        <v>116667031.42059027</v>
+        <v>110992048.4803422</v>
       </c>
       <c r="G10">
-        <v>169120550.01285332</v>
+        <v>124849358.7172148</v>
+      </c>
+      <c r="H10">
+        <v>180981653.15347975</v>
       </c>
     </row>
     <row r="11">
@@ -565,22 +578,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>3239071601</v>
+        <v>4098104719</v>
       </c>
       <c r="C14">
-        <v>2884802030</v>
+        <v>3466240696.277984</v>
       </c>
       <c r="D14">
-        <v>2928349938.4489517</v>
+        <v>3087144282</v>
       </c>
       <c r="E14">
-        <v>2041664001.0959883</v>
+        <v>3133726876.0780587</v>
       </c>
       <c r="F14">
-        <v>2268637187.8824725</v>
+        <v>2184854094.160746</v>
       </c>
       <c r="G14">
-        <v>1422644695.4326298</v>
+        <v>2427745821.765756</v>
+      </c>
+      <c r="H14">
+        <v>1522420479.4145825</v>
       </c>
     </row>
     <row r="15">
@@ -598,22 +614,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>1107941594</v>
+        <v>1356679878</v>
       </c>
       <c r="C17">
-        <v>1098706747</v>
+        <v>1185645986.0400288</v>
       </c>
       <c r="D17">
-        <v>822122286.5783466</v>
+        <v>1175770891</v>
       </c>
       <c r="E17">
-        <v>1377086352.8854284</v>
+        <v>879781023.1102009</v>
       </c>
       <c r="F17">
-        <v>1742393837.9106324</v>
+        <v>1473666947.4014807</v>
       </c>
       <c r="G17">
-        <v>544201778.1973022</v>
+        <v>1864594912.9513605</v>
+      </c>
+      <c r="H17">
+        <v>582368833.7090063</v>
       </c>
     </row>
     <row r="18">
@@ -626,22 +645,25 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>5508668</v>
+        <v>19098497</v>
       </c>
       <c r="C19">
-        <v>7291500</v>
+        <v>5895013.002487885</v>
       </c>
       <c r="D19">
-        <v>5410235.554415809</v>
+        <v>7802932</v>
       </c>
       <c r="E19">
-        <v>17600227.166002158</v>
+        <v>5789677.094318163</v>
       </c>
       <c r="F19">
-        <v>2601399.56947868</v>
+        <v>18834601.75678099</v>
       </c>
       <c r="G19">
-        <v>10882555.389442923</v>
+        <v>2783846.1651243465</v>
+      </c>
+      <c r="H19">
+        <v>11645792.689096645</v>
       </c>
     </row>
     <row r="20">
@@ -654,30 +676,33 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>105044596</v>
+        <v>134767258</v>
       </c>
       <c r="C21">
-        <v>109951308</v>
+        <v>112411795.2399903</v>
       </c>
       <c r="D21">
-        <v>91708514.43011148</v>
+        <v>117663398</v>
       </c>
       <c r="E21">
-        <v>124425753.5619872</v>
+        <v>98140400.72924253</v>
       </c>
       <c r="F21">
-        <v>127926248.36473411</v>
+        <v>133152231.19132753</v>
       </c>
       <c r="G21">
-        <v>130348573.41507238</v>
+        <v>136898229.74802658</v>
+      </c>
+      <c r="H21">
+        <v>139490442.17905277</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="G22">
-        <v>193232123.68341836</v>
+      <c r="H22">
+        <v>206784268.2862896</v>
       </c>
     </row>
     <row r="23">
@@ -690,22 +715,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>5963584353</v>
+        <v>7370479946</v>
       </c>
       <c r="C24">
-        <v>5543204540</v>
+        <v>6381834465.676331</v>
       </c>
       <c r="D24">
-        <v>5280022693.90335</v>
+        <v>5932009226</v>
       </c>
       <c r="E24">
-        <v>5375885038.684612</v>
+        <v>5650331883.13243</v>
       </c>
       <c r="F24">
-        <v>5757892880.95841</v>
+        <v>5752917439.011731</v>
       </c>
       <c r="G24">
-        <v>4044358391.0422244</v>
+        <v>6161717024.910969</v>
+      </c>
+      <c r="H24">
+        <v>4328005481.890521</v>
       </c>
     </row>
     <row r="25">
@@ -741,19 +769,22 @@
         <v>296723</v>
       </c>
       <c r="C30">
-        <v>326514</v>
+        <v>317533.3752437454</v>
       </c>
       <c r="D30">
-        <v>340741.2325360387</v>
+        <v>349416</v>
       </c>
       <c r="E30">
-        <v>427401.7201888516</v>
+        <v>364638.78314752236</v>
       </c>
       <c r="F30">
-        <v>28582.37911392781</v>
+        <v>457377.1187152627</v>
       </c>
       <c r="G30">
-        <v>47098.34057768723</v>
+        <v>30586.97611085703</v>
+      </c>
+      <c r="H30">
+        <v>50401.53628809523</v>
       </c>
     </row>
     <row r="31">
@@ -791,22 +822,25 @@
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
       <c r="B37">
-        <v>109219761</v>
+        <v>116880520</v>
       </c>
       <c r="C37">
-        <v>109219761</v>
+        <v>116879781.32347405</v>
       </c>
       <c r="D37">
-        <v>109213832.13643895</v>
+        <v>116880520</v>
       </c>
       <c r="E37">
-        <v>109221782.32533361</v>
+        <v>116873436.64490886</v>
       </c>
       <c r="F37">
-        <v>109213832.13643895</v>
+        <v>116881944.41246833</v>
       </c>
       <c r="G37">
-        <v>110701086.20433472</v>
+        <v>116873436.64490886</v>
+      </c>
+      <c r="H37">
+        <v>118464997.81146465</v>
       </c>
     </row>
     <row r="38">
@@ -819,22 +853,25 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>4554464414</v>
+        <v>5154303350</v>
       </c>
       <c r="C39">
-        <v>4317970735</v>
+        <v>4873887288.160833</v>
       </c>
       <c r="D39">
-        <v>3169147764.2265725</v>
+        <v>4620836551</v>
       </c>
       <c r="E39">
-        <v>1994798210.3900828</v>
+        <v>3391412820.108428</v>
       </c>
       <c r="F39">
-        <v>1629638555.9857984</v>
+        <v>2134701417.4005587</v>
       </c>
       <c r="G39">
-        <v>1311991684.8129318</v>
+        <v>1743931650.426539</v>
+      </c>
+      <c r="H39">
+        <v>1404006928.921514</v>
       </c>
     </row>
     <row r="40">
@@ -847,22 +884,25 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>5720107</v>
+        <v>5938427</v>
       </c>
       <c r="C41">
-        <v>5790650</v>
+        <v>6121281.068421979</v>
       </c>
       <c r="D41">
-        <v>5083202.150705923</v>
+        <v>6196811</v>
       </c>
       <c r="E41">
-        <v>4023944.092046661</v>
+        <v>5439707.525065187</v>
       </c>
       <c r="F41">
-        <v>920900.3694145319</v>
+        <v>4306159.446149118</v>
       </c>
       <c r="G41">
-        <v>642125.1376565831</v>
+        <v>985486.8094600295</v>
+      </c>
+      <c r="H41">
+        <v>687159.9515000505</v>
       </c>
     </row>
     <row r="42">
@@ -870,22 +910,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>13963541</v>
+        <v>18024532</v>
       </c>
       <c r="C42">
-        <v>71678061</v>
+        <v>14942860.189754162</v>
       </c>
       <c r="D42">
-        <v>539441448.9858816</v>
+        <v>76705616</v>
       </c>
       <c r="E42">
-        <v>313828212.1583041</v>
+        <v>577274643.4986963</v>
       </c>
       <c r="F42">
-        <v>3254961.10382452</v>
+        <v>335838244.6030019</v>
       </c>
       <c r="G42">
-        <v>37563875.56810069</v>
+        <v>3483244.59372717</v>
+      </c>
+      <c r="H42">
+        <v>40198380.96937237</v>
       </c>
     </row>
     <row r="43">
@@ -893,22 +936,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
-        <v>40572335</v>
+        <v>51495595</v>
       </c>
       <c r="C43">
-        <v>55704641</v>
+        <v>43417835.73929202</v>
       </c>
       <c r="D43">
-        <v>51871259.12708406</v>
+        <v>59611808</v>
       </c>
       <c r="E43">
-        <v>42190884.25208104</v>
+        <v>55509198.77719603</v>
       </c>
       <c r="F43">
-        <v>26542765.11500288</v>
+        <v>45149900.34841073</v>
       </c>
       <c r="G43">
-        <v>21573327.49358818</v>
+        <v>28404315.793749746</v>
+      </c>
+      <c r="H43">
+        <v>23086351.561145395</v>
       </c>
     </row>
     <row r="44">
@@ -931,22 +977,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>4724236881</v>
+        <v>5346939147</v>
       </c>
       <c r="C47">
-        <v>4560690362</v>
+        <v>5055566579.857019</v>
       </c>
       <c r="D47">
-        <v>3875098247.859219</v>
+        <v>4880580722</v>
       </c>
       <c r="E47">
-        <v>2464490434.938037</v>
+        <v>4146874445.337442</v>
       </c>
       <c r="F47">
-        <v>1769599597.0895932</v>
+        <v>2637335043.3293037</v>
       </c>
       <c r="G47">
-        <v>1482519197.5571897</v>
+        <v>1893708721.2444956</v>
+      </c>
+      <c r="H47">
+        <v>1586494220.7512848</v>
       </c>
     </row>
     <row r="48">
@@ -954,22 +1003,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>10687821234</v>
+        <v>12717419093</v>
       </c>
       <c r="C48">
-        <v>10103894902</v>
+        <v>11437401045.53335</v>
       </c>
       <c r="D48">
-        <v>9155120941.76257</v>
+        <v>10812589948</v>
       </c>
       <c r="E48">
-        <v>7840375473.622649</v>
+        <v>9797206328.469872</v>
       </c>
       <c r="F48">
-        <v>7527492478.048003</v>
+        <v>8390252482.341035</v>
       </c>
       <c r="G48">
-        <v>5720109712.282832</v>
+        <v>8055425746.155464</v>
+      </c>
+      <c r="H48">
+        <v>6121283970.928095</v>
       </c>
     </row>
     <row r="49">
@@ -982,22 +1034,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>2285265074</v>
+        <v>2754802611</v>
       </c>
       <c r="C50">
-        <v>2672252168</v>
+        <v>2445539888.292676</v>
       </c>
       <c r="D50">
-        <v>2517262665.077595</v>
+        <v>2859686008</v>
       </c>
       <c r="E50">
-        <v>2193281007.243188</v>
+        <v>2693808401.833207</v>
       </c>
       <c r="F50">
-        <v>1619155083.643712</v>
+        <v>2347104609.645801</v>
       </c>
       <c r="G50">
-        <v>2160823932.5147924</v>
+        <v>1732712930.0811088</v>
+      </c>
+      <c r="H50">
+        <v>2312371189.9612947</v>
       </c>
     </row>
     <row r="51">
@@ -1010,22 +1065,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>808458981</v>
+        <v>1420324395</v>
       </c>
       <c r="C52">
-        <v>1044305288</v>
+        <v>865159455.0575757</v>
       </c>
       <c r="D52">
-        <v>766371622.3223252</v>
+        <v>1117553670</v>
       </c>
       <c r="E52">
-        <v>230749325.74487388</v>
+        <v>820120340.9477285</v>
       </c>
       <c r="F52">
-        <v>453490331.7558045</v>
+        <v>246932702.34861565</v>
       </c>
       <c r="G52">
-        <v>443054102.44613063</v>
+        <v>485295429.3493476</v>
+      </c>
+      <c r="H52">
+        <v>474127265.3798594</v>
       </c>
     </row>
     <row r="53">
@@ -1038,33 +1096,36 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>29217603</v>
+        <v>27312757</v>
       </c>
       <c r="C54">
-        <v>17360093</v>
+        <v>31266750.798292622</v>
       </c>
       <c r="D54">
-        <v>16798243.160060823</v>
+        <v>18577715</v>
       </c>
       <c r="E54">
-        <v>4846803.380973116</v>
+        <v>17976371.392778024</v>
       </c>
       <c r="F54">
-        <v>2469515.258747572</v>
+        <v>5186729.160540943</v>
       </c>
       <c r="G54">
-        <v>1665411.0570678483</v>
+        <v>2642712.2782057603</v>
+      </c>
+      <c r="H54">
+        <v>1782213.0206253233</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
-      <c r="F55">
-        <v>249048391.90635005</v>
-      </c>
       <c r="G55">
-        <v>1239515.2347039992</v>
+        <v>266515155.48525196</v>
+      </c>
+      <c r="H55">
+        <v>1326447.414395258</v>
       </c>
     </row>
     <row r="56">
@@ -1092,39 +1153,45 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>189083961</v>
+        <v>394770061</v>
       </c>
       <c r="C60">
-        <v>198665353</v>
+        <v>202345178.30025554</v>
       </c>
       <c r="D60">
-        <v>317509703.31346923</v>
+        <v>212599894</v>
       </c>
       <c r="E60">
-        <v>291844348.148298</v>
+        <v>339777933.51296026</v>
       </c>
       <c r="F60">
-        <v>168035067.27473703</v>
+        <v>312312563.95136136</v>
       </c>
       <c r="G60">
-        <v>158401395.34212792</v>
+        <v>179820041.1530521</v>
+      </c>
+      <c r="H60">
+        <v>169510721.1315091</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="C61">
-        <v>6238231</v>
-      </c>
-      <c r="E61">
-        <v>4207342.630376195</v>
+      <c r="B61">
+        <v>12540416</v>
+      </c>
+      <c r="D61">
+        <v>6675785</v>
       </c>
       <c r="F61">
-        <v>33172895.231983654</v>
+        <v>4502420.460261763</v>
       </c>
       <c r="G61">
-        <v>20964759.37812795</v>
+        <v>35499443.55381591</v>
+      </c>
+      <c r="H61">
+        <v>22435102.120529696</v>
       </c>
     </row>
     <row r="62">
@@ -1132,22 +1199,25 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>24266092</v>
+        <v>19224926</v>
       </c>
       <c r="C62">
-        <v>22543266</v>
+        <v>25967970.45303279</v>
       </c>
       <c r="D62">
-        <v>21769460.72071323</v>
+        <v>24124468</v>
       </c>
       <c r="E62">
-        <v>13231727.727605175</v>
+        <v>23296240.39890474</v>
       </c>
       <c r="F62">
-        <v>9435436.080487762</v>
+        <v>14159721.914555747</v>
       </c>
       <c r="G62">
-        <v>6557246.772762101</v>
+        <v>10097181.093254972</v>
+      </c>
+      <c r="H62">
+        <v>7017132.814312698</v>
       </c>
     </row>
     <row r="63">
@@ -1155,22 +1225,25 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
-        <v>6079648</v>
+        <v>19062406</v>
       </c>
       <c r="C63">
-        <v>15696746</v>
+        <v>6506038.122201132</v>
       </c>
       <c r="D63">
-        <v>4983746.036190092</v>
+        <v>16797567</v>
       </c>
       <c r="E63">
-        <v>2385466.291228759</v>
+        <v>5333276.153951925</v>
       </c>
       <c r="F63">
-        <v>14894793.36447277</v>
+        <v>2552768.6191634866</v>
       </c>
       <c r="G63">
-        <v>34618711.16607765</v>
+        <v>15939425.021246014</v>
+      </c>
+      <c r="H63">
+        <v>37046660.36388475</v>
       </c>
     </row>
     <row r="64">
@@ -1188,22 +1261,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>3342371359</v>
+        <v>4648037572</v>
       </c>
       <c r="C66">
-        <v>3977061145</v>
+        <v>3576785281.0240335</v>
       </c>
       <c r="D66">
-        <v>3644695440.630354</v>
+        <v>4256015107</v>
       </c>
       <c r="E66">
-        <v>2740546021.166543</v>
+        <v>3900312564.2395306</v>
       </c>
       <c r="F66">
-        <v>2549701514.5162954</v>
+        <v>2932751516.1003003</v>
       </c>
       <c r="G66">
-        <v>2827325073.911791</v>
+        <v>2728522318.015283</v>
+      </c>
+      <c r="H66">
+        <v>3025616732.2064114</v>
       </c>
     </row>
     <row r="67">
@@ -1216,22 +1292,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>737525496</v>
+        <v>815642694</v>
       </c>
       <c r="C68">
-        <v>785126663</v>
+        <v>789251119.9778833</v>
       </c>
       <c r="D68">
-        <v>740492962.8720428</v>
+        <v>840196056</v>
       </c>
       <c r="E68">
-        <v>480858587.7520682</v>
+        <v>792426707.2151508</v>
       </c>
       <c r="F68">
-        <v>296634374.97273123</v>
+        <v>514583131.01395905</v>
       </c>
       <c r="G68">
-        <v>164765155.82966363</v>
+        <v>317438534.5875114</v>
+      </c>
+      <c r="H68">
+        <v>176320797.69062313</v>
       </c>
     </row>
     <row r="69">
@@ -1244,13 +1323,16 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B70">
-        <v>751268661</v>
+        <v>791155999</v>
       </c>
       <c r="C70">
-        <v>661821983</v>
+        <v>803958148.314014</v>
       </c>
       <c r="D70">
-        <v>433366538.54679525</v>
+        <v>708242690</v>
+      </c>
+      <c r="E70">
+        <v>463760273.73160356</v>
       </c>
     </row>
     <row r="71">
@@ -1267,7 +1349,7 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>0</v>
       </c>
     </row>
@@ -1306,22 +1388,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>26746860</v>
+        <v>30398600</v>
       </c>
       <c r="C80">
-        <v>24535452</v>
+        <v>28622724.67241139</v>
       </c>
       <c r="D80">
-        <v>25041362.252689164</v>
+        <v>26256387</v>
       </c>
       <c r="E80">
-        <v>22058340.573794704</v>
+        <v>26797613.52102031</v>
       </c>
       <c r="F80">
-        <v>13571929.891180262</v>
+        <v>23605380.55584868</v>
       </c>
       <c r="G80">
-        <v>10288317.507368095</v>
+        <v>14523783.821671886</v>
+      </c>
+      <c r="H80">
+        <v>11009878.51866525</v>
       </c>
     </row>
     <row r="81">
@@ -1334,22 +1419,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>526819709</v>
+        <v>618286382</v>
       </c>
       <c r="C82">
-        <v>446727170</v>
+        <v>563767690.2151089</v>
       </c>
       <c r="D82">
-        <v>335807328.2435481</v>
+        <v>478060960</v>
       </c>
       <c r="E82">
-        <v>465397412.6707419</v>
+        <v>359358844.33885527</v>
       </c>
       <c r="F82">
-        <v>597400666.4414443</v>
+        <v>498037601.65220404</v>
       </c>
       <c r="G82">
-        <v>456280039.70984966</v>
+        <v>639298773.5632719</v>
+      </c>
+      <c r="H82">
+        <v>488280790.7220497</v>
       </c>
     </row>
     <row r="83">
@@ -1362,22 +1450,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>2042360726</v>
+        <v>2255483675</v>
       </c>
       <c r="C84">
-        <v>1918211268</v>
+        <v>2185599683.1794176</v>
       </c>
       <c r="D84">
-        <v>1534708191.9150753</v>
+        <v>2052756093</v>
       </c>
       <c r="E84">
-        <v>968314340.9966049</v>
+        <v>1642343438.80663</v>
       </c>
       <c r="F84">
-        <v>907606971.3053557</v>
+        <v>1036226113.2220118</v>
       </c>
       <c r="G84">
-        <v>631333513.0468814</v>
+        <v>971261091.972455</v>
+      </c>
+      <c r="H84">
+        <v>675611466.9313382</v>
       </c>
     </row>
     <row r="85">
@@ -1390,22 +1481,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>5199468670</v>
+        <v>5685777228</v>
       </c>
       <c r="C86">
-        <v>4113914741</v>
+        <v>5564128282.132521</v>
       </c>
       <c r="D86">
-        <v>3959125254.2183757</v>
+        <v>4402468125</v>
       </c>
       <c r="E86">
-        <v>3940878014.545797</v>
+        <v>4236794602.995765</v>
       </c>
       <c r="F86">
-        <v>3846772967.762178</v>
+        <v>4217267611.1477604</v>
       </c>
       <c r="G86">
-        <v>2261451125.3241606</v>
+        <v>4116562599.629701</v>
+      </c>
+      <c r="H86">
+        <v>2420055771.7903466</v>
       </c>
     </row>
     <row r="87">
@@ -1416,7 +1510,7 @@
         <v>273350000</v>
       </c>
       <c r="C87">
-        <v>218650000</v>
+        <v>273350000</v>
       </c>
       <c r="D87">
         <v>218650000</v>
@@ -1428,6 +1522,9 @@
         <v>218650000</v>
       </c>
       <c r="G87">
+        <v>218650000</v>
+      </c>
+      <c r="H87">
         <v>218650000</v>
       </c>
     </row>
@@ -1436,22 +1533,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>1402298302</v>
+        <v>1520964563</v>
       </c>
       <c r="C88">
-        <v>1402298302</v>
+        <v>1519818244.644031</v>
       </c>
       <c r="D88">
-        <v>1402210179.3073454</v>
+        <v>1515993088</v>
       </c>
       <c r="E88">
-        <v>1402328289.7792747</v>
+        <v>1515887610.9490798</v>
       </c>
       <c r="F88">
-        <v>1402210179.3073454</v>
+        <v>1516014004.9825835</v>
       </c>
       <c r="G88">
-        <v>1402210179.3073454</v>
+        <v>1515887610.9490798</v>
+      </c>
+      <c r="H88">
+        <v>1515887610.9490798</v>
       </c>
     </row>
     <row r="89">
@@ -1473,8 +1573,8 @@
       <c r="A92" t="str">
         <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
       </c>
-      <c r="B92">
-        <v>-62663610</v>
+      <c r="C92">
+        <v>-67058460.5448776</v>
       </c>
     </row>
     <row r="93">
@@ -1487,7 +1587,13 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>1090249826</v>
+        <v>1166720794</v>
+      </c>
+      <c r="C94">
+        <v>1166713423.3230526</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1505,64 +1611,76 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>381951146</v>
+        <v>-24031145</v>
       </c>
       <c r="C97">
-        <v>383282125</v>
+        <v>408738913.2881394</v>
       </c>
       <c r="D97">
-        <v>-23467639.88497336</v>
+        <v>-23252117</v>
       </c>
       <c r="E97">
-        <v>382286667.9387798</v>
+        <v>-25113519.685633846</v>
       </c>
       <c r="F97">
-        <v>-12806840.809243234</v>
+        <v>409097966.7275056</v>
       </c>
       <c r="G97">
-        <v>-8209021.198573303</v>
+        <v>-13705035.97081569</v>
+      </c>
+      <c r="H97">
+        <v>-8784752.811984368</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
+      <c r="B98">
+        <v>433417947</v>
+      </c>
+      <c r="D98">
+        <v>433417947</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>1409698679</v>
+        <v>1508576037</v>
       </c>
       <c r="C99">
-        <v>1409698679</v>
+        <v>1508566506.8751638</v>
       </c>
       <c r="D99">
-        <v>1409622154.6964736</v>
+        <v>1508576037</v>
       </c>
       <c r="E99">
-        <v>1409724758.4020011</v>
+        <v>1508484615.615009</v>
       </c>
       <c r="F99">
-        <v>1379432472.0773277</v>
+        <v>1508594415.3303282</v>
       </c>
       <c r="G99">
-        <v>45451538.49826266</v>
+        <v>1476177609.351272</v>
+      </c>
+      <c r="H99">
+        <v>48639237.367424764</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
-        <v>404988232.3373406</v>
-      </c>
-      <c r="F100">
-        <v>404988232.3373406</v>
+      <c r="E100">
+        <v>433391682.97730184</v>
       </c>
       <c r="G100">
-        <v>395494270.70636904</v>
+        <v>433391682.97730184</v>
+      </c>
+      <c r="H100">
+        <v>423231871.7017451</v>
       </c>
     </row>
     <row r="101">
@@ -1580,22 +1698,25 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>699985635</v>
+        <v>749083170</v>
       </c>
       <c r="C103">
-        <v>527878531</v>
+        <v>749078437.8146838</v>
       </c>
       <c r="D103">
-        <v>495062074.6868455</v>
+        <v>564904340</v>
       </c>
       <c r="E103">
-        <v>454331993.38136584</v>
+        <v>529782765.51020724</v>
       </c>
       <c r="F103">
-        <v>207854158.01075664</v>
+        <v>486196120.08372825</v>
       </c>
       <c r="G103">
-        <v>84120158.04372747</v>
+        <v>222431804.58408126</v>
+      </c>
+      <c r="H103">
+        <v>90019842.44450913</v>
       </c>
     </row>
     <row r="104">
@@ -1603,22 +1724,25 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>4598692</v>
+        <v>57695862</v>
       </c>
       <c r="C104">
-        <v>172107104</v>
+        <v>4921216.732327491</v>
       </c>
       <c r="D104">
-        <v>52060253.075344056</v>
+        <v>184178830</v>
       </c>
       <c r="E104">
-        <v>73556305.04437557</v>
+        <v>55711447.62980145</v>
       </c>
       <c r="F104">
-        <v>246444766.8386503</v>
+        <v>78715104.02361499</v>
       </c>
       <c r="G104">
-        <v>123733999.96702918</v>
+        <v>263728927.7387816</v>
+      </c>
+      <c r="H104">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="105">
@@ -1626,19 +1750,22 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B105">
-        <v>103620479</v>
+        <v>128120618</v>
       </c>
       <c r="C105">
-        <v>94707748</v>
+        <v>110887799.19737817</v>
       </c>
       <c r="D105">
-        <v>16592054.99876456</v>
+        <v>101350623</v>
       </c>
       <c r="E105">
-        <v>190637096.91370484</v>
+        <v>17755722.427946497</v>
       </c>
       <c r="F105">
-        <v>223411024.4641752</v>
+        <v>204007241.87096283</v>
+      </c>
+      <c r="G105">
+        <v>239079736.53802547</v>
       </c>
     </row>
     <row r="106">
@@ -1646,22 +1773,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>5303089149</v>
+        <v>5813897846</v>
       </c>
       <c r="C106">
-        <v>4208622489</v>
+        <v>5675016081.329899</v>
       </c>
       <c r="D106">
-        <v>3975717309.21714</v>
+        <v>4503818748</v>
       </c>
       <c r="E106">
-        <v>4131515111.4595017</v>
+        <v>4254550325.423712</v>
       </c>
       <c r="F106">
-        <v>4070183992.226353</v>
+        <v>4421274853.0187235</v>
       </c>
       <c r="G106">
-        <v>2261451125.3241606</v>
+        <v>4355642336.1677265</v>
+      </c>
+      <c r="H106">
+        <v>2420055771.7903466</v>
       </c>
     </row>
     <row r="107">
@@ -1669,39 +1799,45 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>10687821234</v>
+        <v>12717419093</v>
       </c>
       <c r="C107">
-        <v>10103894902</v>
+        <v>11437401045.53335</v>
       </c>
       <c r="D107">
-        <v>9155120941.76257</v>
+        <v>10812589948</v>
       </c>
       <c r="E107">
-        <v>7840375473.622649</v>
+        <v>9797206328.469872</v>
       </c>
       <c r="F107">
-        <v>7527492478.048003</v>
+        <v>8390252482.341035</v>
       </c>
       <c r="G107">
-        <v>5720109712.282832</v>
+        <v>8055425746.155464</v>
+      </c>
+      <c r="H107">
+        <v>6121283970.928095</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="C108">
+        <v>-1524038270.1003432</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1712,6 +1848,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1719,27 +1857,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1753,28 +1897,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>2574133611</v>
+        <v>6567859522</v>
       </c>
       <c r="C3">
-        <v>8030720668.18386</v>
+        <v>2754685339</v>
       </c>
       <c r="D3">
-        <v>5286650839.675168</v>
+        <v>8593947349.575623</v>
       </c>
       <c r="E3">
-        <v>2144474470</v>
+        <v>5657424887.37724</v>
       </c>
       <c r="F3">
-        <v>6422701532.69286</v>
+        <v>3932624941</v>
       </c>
       <c r="G3">
-        <v>4202014935.7857223</v>
+        <v>2294889572</v>
       </c>
       <c r="H3">
-        <v>7884045169.210893</v>
+        <v>6873151376.3986635</v>
       </c>
       <c r="I3">
-        <v>8311073424.516557</v>
+        <v>4496719113.060567</v>
+      </c>
+      <c r="J3">
+        <v>8436984909.001596</v>
+      </c>
+      <c r="K3">
+        <v>8893962370.242064</v>
       </c>
     </row>
     <row r="4">
@@ -1797,28 +1947,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-2231365091</v>
+        <v>-5746731997</v>
       </c>
       <c r="C7">
-        <v>-7090141666.944702</v>
+        <v>-2387874769</v>
       </c>
       <c r="D7">
-        <v>-4465449622.273376</v>
+        <v>-7587401766.837309</v>
       </c>
       <c r="E7">
-        <v>-1862872753</v>
+        <v>-4778629531.722763</v>
       </c>
       <c r="F7">
-        <v>-5507463077.742694</v>
+        <v>-3347769918</v>
       </c>
       <c r="G7">
-        <v>-3221652795.408723</v>
+        <v>-1993536093</v>
       </c>
       <c r="H7">
-        <v>-6944724622.030547</v>
+        <v>-5893723574.195272</v>
       </c>
       <c r="I7">
-        <v>-6753154970.781933</v>
+        <v>-3447600239.919317</v>
+      </c>
+      <c r="J7">
+        <v>-7431786040.757554</v>
+      </c>
+      <c r="K7">
+        <v>-7226780840.772249</v>
       </c>
     </row>
     <row r="8">
@@ -1826,28 +1982,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>342768520</v>
+        <v>821127525</v>
       </c>
       <c r="C8">
-        <v>940579001.2391579</v>
+        <v>366810570</v>
       </c>
       <c r="D8">
-        <v>821201217.4017915</v>
+        <v>1006545582.7383143</v>
       </c>
       <c r="E8">
-        <v>281601717</v>
+        <v>878795355.6544777</v>
       </c>
       <c r="F8">
-        <v>915238454.9501661</v>
+        <v>584855023</v>
       </c>
       <c r="G8">
-        <v>980362140.3769994</v>
+        <v>301353479</v>
       </c>
       <c r="H8">
-        <v>939320547.1803446</v>
+        <v>979427802.2033913</v>
       </c>
       <c r="I8">
-        <v>1557918453.7346237</v>
+        <v>1049118873.1412501</v>
+      </c>
+      <c r="J8">
+        <v>1005198868.2440412</v>
+      </c>
+      <c r="K8">
+        <v>1667181529.469815</v>
       </c>
     </row>
     <row r="9">
@@ -1875,28 +2037,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>342768520</v>
+        <v>821127525</v>
       </c>
       <c r="C13">
-        <v>940579001.2391579</v>
+        <v>366810570</v>
       </c>
       <c r="D13">
-        <v>821201217.4017915</v>
+        <v>1006545582.7383143</v>
       </c>
       <c r="E13">
-        <v>281601717</v>
+        <v>878795355.6544777</v>
       </c>
       <c r="F13">
-        <v>915238454.9501661</v>
+        <v>584855023</v>
       </c>
       <c r="G13">
-        <v>980362140.3769994</v>
+        <v>301353479</v>
       </c>
       <c r="H13">
-        <v>939320547.1803446</v>
+        <v>979427802.2033913</v>
       </c>
       <c r="I13">
-        <v>1557918453.7346237</v>
+        <v>1049118873.1412501</v>
+      </c>
+      <c r="J13">
+        <v>1005198868.2440412</v>
+      </c>
+      <c r="K13">
+        <v>1667181529.469815</v>
       </c>
     </row>
     <row r="14"/>
@@ -1905,28 +2073,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-68967084</v>
+        <v>-138734905</v>
       </c>
       <c r="C15">
-        <v>-213396910.3214177</v>
+        <v>-73804489</v>
       </c>
       <c r="D15">
-        <v>-132377923.48050915</v>
+        <v>-228363292.36677513</v>
       </c>
       <c r="E15">
-        <v>-56223357</v>
+        <v>-141662118.71180975</v>
       </c>
       <c r="F15">
-        <v>-126732254.66791885</v>
+        <v>-105934138</v>
       </c>
       <c r="G15">
-        <v>-73876256.33625364</v>
+        <v>-60166907</v>
       </c>
       <c r="H15">
-        <v>-88732582.34292978</v>
+        <v>-135620496.4797275</v>
       </c>
       <c r="I15">
-        <v>-80004285.1161908</v>
+        <v>-79057494.78410085</v>
+      </c>
+      <c r="J15">
+        <v>-94955754.57731305</v>
+      </c>
+      <c r="K15">
+        <v>-85615306.82457043</v>
       </c>
     </row>
     <row r="16">
@@ -1934,28 +2108,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-67307207</v>
+        <v>-160557325</v>
       </c>
       <c r="C16">
-        <v>-211461598.07651392</v>
+        <v>-72028187</v>
       </c>
       <c r="D16">
-        <v>-144093466.31789428</v>
+        <v>-226292248.9044387</v>
       </c>
       <c r="E16">
-        <v>-56676408</v>
+        <v>-154199319.6027673</v>
       </c>
       <c r="F16">
-        <v>-173606708.99655935</v>
+        <v>-118480974</v>
       </c>
       <c r="G16">
-        <v>-111314924.08828647</v>
+        <v>-60651735</v>
       </c>
       <c r="H16">
-        <v>-310182025.34436125</v>
+        <v>-185782444.4772943</v>
       </c>
       <c r="I16">
-        <v>-962505360.4621854</v>
+        <v>-119121886.61059272</v>
+      </c>
+      <c r="J16">
+        <v>-331936336.06945205</v>
+      </c>
+      <c r="K16">
+        <v>-1030009725.5614009</v>
       </c>
     </row>
     <row r="17">
@@ -1968,28 +2148,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>44219373</v>
+        <v>104741568</v>
       </c>
       <c r="C18">
-        <v>259302734.65409932</v>
+        <v>47320954</v>
       </c>
       <c r="D18">
-        <v>213060892.5379512</v>
+        <v>277488676.4580079</v>
       </c>
       <c r="E18">
-        <v>63836703</v>
+        <v>228003708.30714363</v>
       </c>
       <c r="F18">
-        <v>159612225.93152848</v>
+        <v>144150729</v>
       </c>
       <c r="G18">
-        <v>111505792.14031158</v>
+        <v>68314259</v>
       </c>
       <c r="H18">
-        <v>386586748.5269154</v>
+        <v>170806472.13126555</v>
       </c>
       <c r="I18">
-        <v>482070834.4692714</v>
+        <v>119326141.00538427</v>
+      </c>
+      <c r="J18">
+        <v>413699629.2308195</v>
+      </c>
+      <c r="K18">
+        <v>515880397.46024626</v>
       </c>
     </row>
     <row r="19">
@@ -1997,28 +2183,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-77501586</v>
+        <v>-164925662</v>
       </c>
       <c r="C19">
-        <v>-128411406.26824555</v>
+        <v>-82937607</v>
       </c>
       <c r="D19">
-        <v>-92353924.99109651</v>
+        <v>-137417413.7230746</v>
       </c>
       <c r="E19">
-        <v>-39665044</v>
+        <v>-98831076.52399904</v>
       </c>
       <c r="F19">
-        <v>-138062261.63386807</v>
+        <v>-51215927</v>
       </c>
       <c r="G19">
-        <v>-86023018.73684524</v>
+        <v>-42447181</v>
       </c>
       <c r="H19">
-        <v>-63077947.19345335</v>
+        <v>-147745122.32077456</v>
       </c>
       <c r="I19">
-        <v>-236124805.4566794</v>
+        <v>-92056158.39744955</v>
+      </c>
+      <c r="J19">
+        <v>-67501856.86914726</v>
+      </c>
+      <c r="K19">
+        <v>-252685186.033547</v>
       </c>
     </row>
     <row r="20">
@@ -2031,28 +2223,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>173212016</v>
+        <v>461651201</v>
       </c>
       <c r="C21">
-        <v>646611821.2270801</v>
+        <v>185361241</v>
       </c>
       <c r="D21">
-        <v>665436795.1502427</v>
+        <v>691961304.2020338</v>
       </c>
       <c r="E21">
-        <v>192873611</v>
+        <v>712106549.1230453</v>
       </c>
       <c r="F21">
-        <v>636449455.5833483</v>
+        <v>453374713</v>
       </c>
       <c r="G21">
-        <v>820653733.3559257</v>
+        <v>206401915</v>
       </c>
       <c r="H21">
-        <v>863914740.8265156</v>
+        <v>681086211.0568604</v>
       </c>
       <c r="I21">
-        <v>761354837.1688396</v>
+        <v>878209474.3544914</v>
+      </c>
+      <c r="J21">
+        <v>924504549.9589484</v>
+      </c>
+      <c r="K21">
+        <v>814751708.510543</v>
       </c>
     </row>
     <row r="22"/>
@@ -2071,28 +2269,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>9475417</v>
+        <v>32140391</v>
       </c>
       <c r="C25">
-        <v>5645112.254147137</v>
+        <v>10140030</v>
       </c>
       <c r="D25">
-        <v>5407389.948331264</v>
+        <v>6041026.639961069</v>
       </c>
       <c r="E25">
-        <v>1954406</v>
+        <v>5786631.914454654</v>
       </c>
       <c r="F25">
-        <v>8117593.317908744</v>
+        <v>4334798</v>
       </c>
       <c r="G25">
-        <v>8431506.713199612</v>
+        <v>2090826</v>
       </c>
       <c r="H25">
-        <v>137215328.65431422</v>
+        <v>8686912.726993317</v>
       </c>
       <c r="I25">
-        <v>22764886.571836706</v>
+        <v>9022842.128963953</v>
+      </c>
+      <c r="J25">
+        <v>146838790.531183</v>
+      </c>
+      <c r="K25">
+        <v>24361479.46130339</v>
       </c>
     </row>
     <row r="26">
@@ -2100,22 +2304,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-3708931</v>
+        <v>-4456479</v>
       </c>
       <c r="C26">
-        <v>-101457.81183139957</v>
+        <v>-3969078</v>
       </c>
       <c r="D26">
-        <v>-88228.71714351898</v>
+        <v>-108573.45549778451</v>
       </c>
       <c r="E26">
-        <v>-620</v>
+        <v>-94416.5512886001</v>
       </c>
       <c r="F26">
-        <v>-48833.42894870897</v>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>-3628732.2668729695</v>
+        <v>-52258.31337243552</v>
+      </c>
+      <c r="J26">
+        <v>-3883229.8290191917</v>
       </c>
     </row>
     <row r="27">
@@ -2153,28 +2363,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>178978502</v>
+        <v>489335113</v>
       </c>
       <c r="C33">
-        <v>652155475.6693958</v>
+        <v>191532193</v>
       </c>
       <c r="D33">
-        <v>670755956.3814303</v>
+        <v>697893757.386497</v>
       </c>
       <c r="E33">
-        <v>194827397</v>
+        <v>717798764.4862112</v>
       </c>
       <c r="F33">
-        <v>644518215.4723083</v>
+        <v>457709511</v>
       </c>
       <c r="G33">
-        <v>829085240.0691253</v>
+        <v>208492741</v>
       </c>
       <c r="H33">
-        <v>997501337.213957</v>
+        <v>689720865.4704813</v>
       </c>
       <c r="I33">
-        <v>784119723.7406763</v>
+        <v>887232316.4834553</v>
+      </c>
+      <c r="J33">
+        <v>1067460110.6611123</v>
+      </c>
+      <c r="K33">
+        <v>839113187.9718463</v>
       </c>
     </row>
     <row r="34"/>
@@ -2183,28 +2399,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>32057007</v>
+        <v>58137672</v>
       </c>
       <c r="C35">
-        <v>45908046.084784016</v>
+        <v>34305510</v>
       </c>
       <c r="D35">
-        <v>36811772.00416367</v>
+        <v>49127761.66372974</v>
       </c>
       <c r="E35">
-        <v>12308523</v>
+        <v>39393529.36302647</v>
       </c>
       <c r="F35">
-        <v>89767532.19107707</v>
+        <v>30836157</v>
       </c>
       <c r="G35">
-        <v>79017553.40698262</v>
+        <v>13171852</v>
       </c>
       <c r="H35">
-        <v>129333877.13791792</v>
+        <v>96063289.61332378</v>
       </c>
       <c r="I35">
-        <v>131047815.08034521</v>
+        <v>84559371.65916395</v>
+      </c>
+      <c r="J35">
+        <v>138404581.17828062</v>
+      </c>
+      <c r="K35">
+        <v>140238724.4695565</v>
       </c>
     </row>
     <row r="36">
@@ -2212,28 +2434,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-244514329</v>
+        <v>-538928971</v>
       </c>
       <c r="C36">
-        <v>-901103737.4013951</v>
+        <v>-261664754</v>
       </c>
       <c r="D36">
-        <v>-883766628.2208766</v>
+        <v>-964301760.1662784</v>
       </c>
       <c r="E36">
-        <v>-253532870</v>
+        <v>-945748729.9156427</v>
       </c>
       <c r="F36">
-        <v>-870880375.3196902</v>
+        <v>-622337053</v>
       </c>
       <c r="G36">
-        <v>-655226828.2714227</v>
+        <v>-271315862</v>
       </c>
       <c r="H36">
-        <v>-642990413.2022974</v>
+        <v>-931958712.3640603</v>
       </c>
       <c r="I36">
-        <v>-622805599.0828279</v>
+        <v>-701180516.2770625</v>
+      </c>
+      <c r="J36">
+        <v>-688085912.2936072</v>
+      </c>
+      <c r="K36">
+        <v>-666485456.1239717</v>
       </c>
     </row>
     <row r="37">
@@ -2241,28 +2469,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>133776420</v>
+        <v>235048779</v>
       </c>
       <c r="C37">
-        <v>510034267.7191757</v>
+        <v>143159602</v>
       </c>
       <c r="D37">
-        <v>517432267.1969815</v>
+        <v>545805018.548754</v>
       </c>
       <c r="E37">
-        <v>172546219</v>
+        <v>553721869.4306847</v>
       </c>
       <c r="F37">
-        <v>479448215.3358718</v>
+        <v>280761931</v>
       </c>
       <c r="G37">
-        <v>292972957.2797144</v>
+        <v>184648745</v>
       </c>
       <c r="H37">
-        <v>96470931.33800583</v>
+        <v>513073843.51799303</v>
       </c>
       <c r="I37">
-        <v>90803399.2508657</v>
+        <v>313520326.97219074</v>
+      </c>
+      <c r="J37">
+        <v>103236825.05456133</v>
+      </c>
+      <c r="K37">
+        <v>97171806.18871059</v>
       </c>
     </row>
     <row r="38">
@@ -2270,28 +2504,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>100297600</v>
+        <v>243592593</v>
       </c>
       <c r="C38">
-        <v>306994052.07196057</v>
+        <v>107332551</v>
       </c>
       <c r="D38">
-        <v>341233367.3616989</v>
+        <v>328524777.4327025</v>
       </c>
       <c r="E38">
-        <v>126149269</v>
+        <v>365165433.36427975</v>
       </c>
       <c r="F38">
-        <v>342853587.679567</v>
+        <v>146970546</v>
       </c>
       <c r="G38">
-        <v>545848922.4843996</v>
+        <v>134997476</v>
       </c>
       <c r="H38">
-        <v>580315732.4875833</v>
+        <v>366899286.23773795</v>
       </c>
       <c r="I38">
-        <v>383165338.9890592</v>
+        <v>584131498.8377475</v>
+      </c>
+      <c r="J38">
+        <v>621015604.600347</v>
+      </c>
+      <c r="K38">
+        <v>410038262.5061416</v>
       </c>
     </row>
     <row r="39"/>
@@ -2300,16 +2540,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-86786177</v>
+        <v>-159126736</v>
       </c>
       <c r="C40">
-        <v>-230811359.83663595</v>
-      </c>
-      <c r="E40">
-        <v>-118413975</v>
+        <v>-92873427</v>
+      </c>
+      <c r="D40">
+        <v>-246999087.14028126</v>
       </c>
       <c r="F40">
-        <v>-302087470.464411</v>
+        <v>-108307504</v>
+      </c>
+      <c r="G40">
+        <v>-126719623</v>
+      </c>
+      <c r="H40">
+        <v>-323274077.55856365</v>
       </c>
     </row>
     <row r="41">
@@ -2317,22 +2563,28 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
+        <v>-12540416</v>
+      </c>
+      <c r="C41">
         <v>0</v>
       </c>
-      <c r="C41">
-        <v>-6922065.100308207</v>
-      </c>
-      <c r="E41">
+      <c r="D41">
+        <v>-7407537.315805651</v>
+      </c>
+      <c r="F41">
         <v>0</v>
       </c>
-      <c r="F41">
-        <v>-4829336.381903713</v>
+      <c r="G41">
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>-65745888.930072874</v>
-      </c>
-      <c r="I41">
-        <v>-32606540.38515452</v>
+        <v>-5168037.130702047</v>
+      </c>
+      <c r="J41">
+        <v>-70356912.07074085</v>
+      </c>
+      <c r="K41">
+        <v>-34893367.967834</v>
       </c>
     </row>
     <row r="42">
@@ -2340,28 +2592,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-86786177</v>
+        <v>-146586320</v>
       </c>
       <c r="C42">
-        <v>-223889294.73632774</v>
+        <v>-92873427</v>
       </c>
       <c r="D42">
-        <v>-115141947.32797974</v>
+        <v>-239591549.8244756</v>
       </c>
       <c r="E42">
-        <v>-118413975</v>
+        <v>-123217314.35443482</v>
       </c>
       <c r="F42">
-        <v>-297258134.0825073</v>
+        <v>-108307504</v>
       </c>
       <c r="G42">
-        <v>-522399225.53529024</v>
+        <v>-126719623</v>
       </c>
       <c r="H42">
-        <v>-356274104.26018494</v>
+        <v>-318106040.42786163</v>
       </c>
       <c r="I42">
-        <v>-226824798.6368755</v>
+        <v>-559037180.4981053</v>
+      </c>
+      <c r="J42">
+        <v>-381261037.5254988</v>
+      </c>
+      <c r="K42">
+        <v>-242732932.39873546</v>
       </c>
     </row>
     <row r="43">
@@ -2369,28 +2627,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>13511423</v>
+        <v>84465857</v>
       </c>
       <c r="C43">
-        <v>76182692.23532459</v>
+        <v>14459124</v>
       </c>
       <c r="D43">
-        <v>341233367.3616989</v>
+        <v>81525690.29242119</v>
       </c>
       <c r="E43">
-        <v>7735294</v>
+        <v>365165433.36427975</v>
       </c>
       <c r="F43">
-        <v>40766117.21515594</v>
+        <v>38663042</v>
       </c>
       <c r="G43">
-        <v>545848922.4843996</v>
+        <v>8277853</v>
       </c>
       <c r="H43">
-        <v>580315732.4875833</v>
+        <v>43625208.679174244</v>
       </c>
       <c r="I43">
-        <v>383165338.9890592</v>
+        <v>584131498.8377475</v>
+      </c>
+      <c r="J43">
+        <v>621015604.600347</v>
+      </c>
+      <c r="K43">
+        <v>410038262.5061416</v>
       </c>
     </row>
     <row r="44">
@@ -2404,28 +2668,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>13511423</v>
+        <v>84465857</v>
       </c>
       <c r="C46">
-        <v>76182692.23532459</v>
+        <v>14459124</v>
       </c>
       <c r="D46">
-        <v>52060253.075344056</v>
+        <v>81525690.29242119</v>
       </c>
       <c r="E46">
-        <v>7735294</v>
+        <v>55711447.62980145</v>
       </c>
       <c r="F46">
-        <v>40766117.21515594</v>
+        <v>38663042</v>
       </c>
       <c r="G46">
-        <v>95782262.511805</v>
+        <v>8277853</v>
       </c>
       <c r="H46">
-        <v>246444766.8386503</v>
+        <v>43625208.679174244</v>
       </c>
       <c r="I46">
-        <v>123733999.96702918</v>
+        <v>102499857.1187805</v>
+      </c>
+      <c r="J46">
+        <v>263728927.7387816</v>
+      </c>
+      <c r="K46">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="47">
@@ -2433,16 +2703,22 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>8912731</v>
+        <v>26769995</v>
       </c>
       <c r="C47">
-        <v>-95927596.84348026</v>
-      </c>
-      <c r="E47">
-        <v>-89181325</v>
+        <v>9537877</v>
+      </c>
+      <c r="D47">
+        <v>-102655384.33060984</v>
       </c>
       <c r="F47">
-        <v>-32790187.829219636</v>
+        <v>-99121822</v>
+      </c>
+      <c r="G47">
+        <v>-95436572</v>
+      </c>
+      <c r="H47">
+        <v>-35089895.34444075</v>
       </c>
     </row>
     <row r="48">
@@ -2450,28 +2726,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>4598692</v>
+        <v>57695862</v>
       </c>
       <c r="C48">
-        <v>172110289.07880485</v>
+        <v>4921247</v>
       </c>
       <c r="D48">
-        <v>52060253.075344056</v>
+        <v>184181074.62303105</v>
       </c>
       <c r="E48">
-        <v>96916619</v>
+        <v>55711447.62980145</v>
       </c>
       <c r="F48">
-        <v>73556305.04437557</v>
+        <v>137784864</v>
       </c>
       <c r="G48">
-        <v>95782262.511805</v>
+        <v>103714425</v>
       </c>
       <c r="H48">
-        <v>246444766.8386503</v>
+        <v>78715104.02361499</v>
       </c>
       <c r="I48">
-        <v>123733999.96702918</v>
+        <v>102499857.1187805</v>
+      </c>
+      <c r="J48">
+        <v>263728927.7387816</v>
+      </c>
+      <c r="K48">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="49"/>
@@ -2480,40 +2762,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>48518198</v>
+        <v>105403359</v>
       </c>
       <c r="C50">
-        <v>157803778.04255706</v>
+        <v>51920974.01173599</v>
       </c>
       <c r="D50">
-        <v>78272145.85962306</v>
+        <v>168871190.53146532</v>
       </c>
       <c r="E50">
-        <v>37668748</v>
+        <v>83761685.6879206</v>
       </c>
       <c r="F50">
-        <v>129514790.64617644</v>
+        <v>84010958</v>
       </c>
       <c r="G50">
-        <v>92403735.72940288</v>
+        <v>40310608.5259521</v>
       </c>
       <c r="H50">
-        <v>83094054.07858114</v>
+        <v>138598182.87718672</v>
       </c>
       <c r="I50">
-        <v>50911249.47339942</v>
+        <v>98884380.689358</v>
+      </c>
+      <c r="J50">
+        <v>88921773.68878779</v>
+      </c>
+      <c r="K50">
+        <v>54481859.792348</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2524,6 +2812,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2531,27 +2821,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2565,16 +2861,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>2574133611</v>
+        <v>3813174183</v>
       </c>
       <c r="C3">
-        <v>2744069828.508692</v>
+        <v>2754685339</v>
+      </c>
+      <c r="D3">
+        <v>2936522462.1983824</v>
       </c>
       <c r="E3">
-        <v>2144474470</v>
+        <v>1724799946.3772402</v>
       </c>
       <c r="F3">
-        <v>2220686596.9071374</v>
+        <v>1637735369</v>
+      </c>
+      <c r="G3">
+        <v>2294889572</v>
+      </c>
+      <c r="H3">
+        <v>2376432263.3380966</v>
       </c>
     </row>
     <row r="4">
@@ -2597,16 +2902,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-2231365091</v>
+        <v>-3358857228</v>
       </c>
       <c r="C7">
-        <v>-2624692044.6713257</v>
+        <v>-2387874769</v>
+      </c>
+      <c r="D7">
+        <v>-2808772235.114546</v>
       </c>
       <c r="E7">
-        <v>-1862872753</v>
+        <v>-1430859613.722763</v>
       </c>
       <c r="F7">
-        <v>-2285810282.333971</v>
+        <v>-1354233825</v>
+      </c>
+      <c r="G7">
+        <v>-1993536093</v>
+      </c>
+      <c r="H7">
+        <v>-2446123334.2759557</v>
       </c>
     </row>
     <row r="8">
@@ -2614,16 +2928,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>342768520</v>
+        <v>454316955</v>
       </c>
       <c r="C8">
-        <v>119377783.83736646</v>
+        <v>366810570</v>
+      </c>
+      <c r="D8">
+        <v>127750227.08383656</v>
       </c>
       <c r="E8">
-        <v>281601717</v>
+        <v>293940332.6544777</v>
       </c>
       <c r="F8">
-        <v>-65123685.42683327</v>
+        <v>283501544</v>
+      </c>
+      <c r="G8">
+        <v>301353479</v>
+      </c>
+      <c r="H8">
+        <v>-69691070.93785882</v>
       </c>
     </row>
     <row r="9">
@@ -2651,16 +2974,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>342768520</v>
+        <v>454316955</v>
       </c>
       <c r="C13">
-        <v>119377783.83736646</v>
+        <v>366810570</v>
+      </c>
+      <c r="D13">
+        <v>127750227.08383656</v>
       </c>
       <c r="E13">
-        <v>281601717</v>
+        <v>293940332.6544777</v>
       </c>
       <c r="F13">
-        <v>-65123685.42683327</v>
+        <v>283501544</v>
+      </c>
+      <c r="G13">
+        <v>301353479</v>
+      </c>
+      <c r="H13">
+        <v>-69691070.93785882</v>
       </c>
     </row>
     <row r="14"/>
@@ -2669,16 +3001,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-68967084</v>
+        <v>-64930416</v>
       </c>
       <c r="C15">
-        <v>-81018986.84090854</v>
+        <v>-73804489</v>
+      </c>
+      <c r="D15">
+        <v>-86701173.65496537</v>
       </c>
       <c r="E15">
-        <v>-56223357</v>
+        <v>-35727980.711809754</v>
       </c>
       <c r="F15">
-        <v>-52855998.3316652</v>
+        <v>-45767231</v>
+      </c>
+      <c r="G15">
+        <v>-60166907</v>
+      </c>
+      <c r="H15">
+        <v>-56563001.69562666</v>
       </c>
     </row>
     <row r="16">
@@ -2686,16 +3027,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-67307207</v>
+        <v>-88529138</v>
       </c>
       <c r="C16">
-        <v>-67368131.75861964</v>
+        <v>-72028187</v>
+      </c>
+      <c r="D16">
+        <v>-72092929.30167142</v>
       </c>
       <c r="E16">
-        <v>-56676408</v>
+        <v>-35718345.60276729</v>
       </c>
       <c r="F16">
-        <v>-62291784.90827288</v>
+        <v>-57829239</v>
+      </c>
+      <c r="G16">
+        <v>-60651735</v>
+      </c>
+      <c r="H16">
+        <v>-66660557.86670157</v>
       </c>
     </row>
     <row r="17">
@@ -2708,16 +3058,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>44219373</v>
+        <v>57420614</v>
       </c>
       <c r="C18">
-        <v>46241842.116148114</v>
+        <v>47320954</v>
+      </c>
+      <c r="D18">
+        <v>49484968.15086424</v>
       </c>
       <c r="E18">
-        <v>63836703</v>
+        <v>83852979.30714363</v>
       </c>
       <c r="F18">
-        <v>48106433.791216895</v>
+        <v>75836470</v>
+      </c>
+      <c r="G18">
+        <v>68314259</v>
+      </c>
+      <c r="H18">
+        <v>51480331.125881284</v>
       </c>
     </row>
     <row r="19">
@@ -2725,16 +3084,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-77501586</v>
+        <v>-81988055</v>
       </c>
       <c r="C19">
-        <v>-36057481.27714904</v>
+        <v>-82937607</v>
+      </c>
+      <c r="D19">
+        <v>-38586337.19907555</v>
       </c>
       <c r="E19">
-        <v>-39665044</v>
+        <v>-47615149.523999035</v>
       </c>
       <c r="F19">
-        <v>-52039242.89702283</v>
+        <v>-8768746</v>
+      </c>
+      <c r="G19">
+        <v>-42447181</v>
+      </c>
+      <c r="H19">
+        <v>-55688963.923325</v>
       </c>
     </row>
     <row r="20">
@@ -2747,16 +3115,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>173212016</v>
+        <v>276289960</v>
       </c>
       <c r="C21">
-        <v>-18824973.92316258</v>
+        <v>185361241</v>
+      </c>
+      <c r="D21">
+        <v>-20145244.921011567</v>
       </c>
       <c r="E21">
-        <v>192873611</v>
+        <v>258731836.12304533</v>
       </c>
       <c r="F21">
-        <v>-184204277.7725774</v>
+        <v>246972798</v>
+      </c>
+      <c r="G21">
+        <v>206401915</v>
+      </c>
+      <c r="H21">
+        <v>-197123263.2976309</v>
       </c>
     </row>
     <row r="22"/>
@@ -2775,16 +3152,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>9475417</v>
+        <v>22000361</v>
       </c>
       <c r="C25">
-        <v>237722.30581587274</v>
+        <v>10140030</v>
+      </c>
+      <c r="D25">
+        <v>254394.7255064156</v>
       </c>
       <c r="E25">
-        <v>1954406</v>
+        <v>1451833.9144546539</v>
       </c>
       <c r="F25">
-        <v>-313913.3952908674</v>
+        <v>2243972</v>
+      </c>
+      <c r="G25">
+        <v>2090826</v>
+      </c>
+      <c r="H25">
+        <v>-335929.4019706361</v>
       </c>
     </row>
     <row r="26">
@@ -2792,13 +3178,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-3708931</v>
+        <v>-487401</v>
       </c>
       <c r="C26">
-        <v>-13229.094687880584</v>
+        <v>-3969078</v>
+      </c>
+      <c r="D26">
+        <v>-14156.904209184417</v>
       </c>
       <c r="E26">
-        <v>-620</v>
+        <v>-94416.5512886001</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2836,16 +3231,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>178978502</v>
+        <v>297802920</v>
       </c>
       <c r="C33">
-        <v>-18600480.712034464</v>
+        <v>191532193</v>
+      </c>
+      <c r="D33">
+        <v>-19905007.09971416</v>
       </c>
       <c r="E33">
-        <v>194827397</v>
+        <v>260089253.48621118</v>
       </c>
       <c r="F33">
-        <v>-184567024.59681702</v>
+        <v>249216770</v>
+      </c>
+      <c r="G33">
+        <v>208492741</v>
+      </c>
+      <c r="H33">
+        <v>-197511451.01297402</v>
       </c>
     </row>
     <row r="34"/>
@@ -2854,16 +3258,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>32057007</v>
+        <v>23832162</v>
       </c>
       <c r="C35">
-        <v>9096274.080620348</v>
+        <v>34305510</v>
+      </c>
+      <c r="D35">
+        <v>9734232.300703272</v>
       </c>
       <c r="E35">
-        <v>12308523</v>
+        <v>8557372.36302647</v>
       </c>
       <c r="F35">
-        <v>10749978.784094453</v>
+        <v>17664305</v>
+      </c>
+      <c r="G35">
+        <v>13171852</v>
+      </c>
+      <c r="H35">
+        <v>11503917.954159826</v>
       </c>
     </row>
     <row r="36">
@@ -2871,16 +3284,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-244514329</v>
+        <v>-277264217</v>
       </c>
       <c r="C36">
-        <v>-17337109.180518508</v>
+        <v>-261664754</v>
+      </c>
+      <c r="D36">
+        <v>-18553030.250635624</v>
       </c>
       <c r="E36">
-        <v>-253532870</v>
+        <v>-323411676.91564274</v>
       </c>
       <c r="F36">
-        <v>-215653547.04826748</v>
+        <v>-351021191</v>
+      </c>
+      <c r="G36">
+        <v>-271315862</v>
+      </c>
+      <c r="H36">
+        <v>-230778196.08699775</v>
       </c>
     </row>
     <row r="37">
@@ -2888,16 +3310,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>133776420</v>
+        <v>91889177</v>
       </c>
       <c r="C37">
-        <v>-7397999.477805793</v>
+        <v>143159602</v>
+      </c>
+      <c r="D37">
+        <v>-7916850.881930709</v>
       </c>
       <c r="E37">
-        <v>172546219</v>
+        <v>272959938.4306847</v>
       </c>
       <c r="F37">
-        <v>186475258.0561574</v>
+        <v>96113186</v>
+      </c>
+      <c r="G37">
+        <v>184648745</v>
+      </c>
+      <c r="H37">
+        <v>199553516.5458023</v>
       </c>
     </row>
     <row r="38">
@@ -2905,16 +3336,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>100297600</v>
+        <v>136260042</v>
       </c>
       <c r="C38">
-        <v>-34239315.28973836</v>
+        <v>107332551</v>
+      </c>
+      <c r="D38">
+        <v>-36640655.931577265</v>
       </c>
       <c r="E38">
-        <v>126149269</v>
+        <v>218194887.36427975</v>
       </c>
       <c r="F38">
-        <v>-202995334.80483258</v>
+        <v>11973070</v>
+      </c>
+      <c r="G38">
+        <v>134997476</v>
+      </c>
+      <c r="H38">
+        <v>-217232212.6000095</v>
       </c>
     </row>
     <row r="39"/>
@@ -2923,10 +3363,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-86786177</v>
-      </c>
-      <c r="E40">
-        <v>-118413975</v>
+        <v>-66253309</v>
+      </c>
+      <c r="C40">
+        <v>-92873427</v>
+      </c>
+      <c r="F40">
+        <v>18412119</v>
+      </c>
+      <c r="G40">
+        <v>-126719623</v>
       </c>
     </row>
     <row r="41">
@@ -2934,9 +3380,15 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
+        <v>-12540416</v>
+      </c>
+      <c r="C41">
         <v>0</v>
       </c>
-      <c r="E41">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>0</v>
       </c>
     </row>
@@ -2945,16 +3397,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-86786177</v>
+        <v>-53712893</v>
       </c>
       <c r="C42">
-        <v>-108747347.408348</v>
+        <v>-92873427</v>
+      </c>
+      <c r="D42">
+        <v>-116374235.47004077</v>
       </c>
       <c r="E42">
-        <v>-118413975</v>
+        <v>-14909810.354434818</v>
       </c>
       <c r="F42">
-        <v>225141091.45278293</v>
+        <v>18412119</v>
+      </c>
+      <c r="G42">
+        <v>-126719623</v>
+      </c>
+      <c r="H42">
+        <v>240931140.07024366</v>
       </c>
     </row>
     <row r="43">
@@ -2962,16 +3423,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>13511423</v>
+        <v>70006733</v>
       </c>
       <c r="C43">
-        <v>-265050675.12637433</v>
+        <v>14459124</v>
+      </c>
+      <c r="D43">
+        <v>-283639743.0718585</v>
       </c>
       <c r="E43">
-        <v>7735294</v>
+        <v>326502391.36427975</v>
       </c>
       <c r="F43">
-        <v>-505082805.2692436</v>
+        <v>30385189</v>
+      </c>
+      <c r="G43">
+        <v>8277853</v>
+      </c>
+      <c r="H43">
+        <v>-540506290.1585732</v>
       </c>
     </row>
     <row r="44">
@@ -2985,16 +3455,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>13511423</v>
+        <v>70006733</v>
       </c>
       <c r="C46">
-        <v>24122439.159980536</v>
+        <v>14459124</v>
+      </c>
+      <c r="D46">
+        <v>25814242.66261974</v>
       </c>
       <c r="E46">
-        <v>7735294</v>
+        <v>17048405.629801452</v>
       </c>
       <c r="F46">
-        <v>-55016145.29664906</v>
+        <v>30385189</v>
+      </c>
+      <c r="G46">
+        <v>8277853</v>
+      </c>
+      <c r="H46">
+        <v>-58874648.43960625</v>
       </c>
     </row>
     <row r="47">
@@ -3002,10 +3481,16 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>8912731</v>
-      </c>
-      <c r="E47">
-        <v>-89181325</v>
+        <v>17232118</v>
+      </c>
+      <c r="C47">
+        <v>9537877</v>
+      </c>
+      <c r="F47">
+        <v>-3685250</v>
+      </c>
+      <c r="G47">
+        <v>-95436572</v>
       </c>
     </row>
     <row r="48">
@@ -3013,16 +3498,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>4598692</v>
+        <v>52774615</v>
       </c>
       <c r="C48">
-        <v>120050036.0034608</v>
+        <v>4921247</v>
+      </c>
+      <c r="D48">
+        <v>128469626.9932296</v>
       </c>
       <c r="E48">
-        <v>96916619</v>
+        <v>-82073416.37019855</v>
       </c>
       <c r="F48">
-        <v>-22225957.46742943</v>
+        <v>34070439</v>
+      </c>
+      <c r="G48">
+        <v>103714425</v>
+      </c>
+      <c r="H48">
+        <v>-23784753.095165506</v>
       </c>
     </row>
     <row r="49"/>
@@ -3031,28 +3525,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>48518198</v>
+        <v>53482384.98826401</v>
       </c>
       <c r="C50">
-        <v>79531632.182934</v>
+        <v>51920974.01173599</v>
+      </c>
+      <c r="D50">
+        <v>85109504.84354472</v>
       </c>
       <c r="E50">
-        <v>37668748</v>
+        <v>-249272.31207939982</v>
       </c>
       <c r="F50">
-        <v>37111054.91677356</v>
+        <v>43700349.4740479</v>
+      </c>
+      <c r="G50">
+        <v>40310608.5259521</v>
+      </c>
+      <c r="H50">
+        <v>39713802.18782872</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3063,6 +3566,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3070,27 +3575,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3104,22 +3615,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>8460379809.18386</v>
+        <v>11229181930.575623</v>
       </c>
       <c r="C3">
-        <v>8030720668.18386</v>
+        <v>9053743116.575623</v>
       </c>
       <c r="D3">
-        <v>7507337436.582306</v>
-      </c>
-      <c r="F3">
-        <v>6422701532.69286</v>
+        <v>8593947349.575623</v>
+      </c>
+      <c r="E3">
+        <v>8033857150.715337</v>
       </c>
       <c r="H3">
-        <v>7884045169.210893</v>
-      </c>
-      <c r="I3">
-        <v>8311073424.516557</v>
+        <v>6873151376.3986635</v>
+      </c>
+      <c r="J3">
+        <v>8436984909.001596</v>
+      </c>
+      <c r="K3">
+        <v>8893962370.242064</v>
       </c>
     </row>
     <row r="4">
@@ -3142,22 +3656,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-7458634004.944702</v>
+        <v>-9986363845.837309</v>
       </c>
       <c r="C7">
-        <v>-7090141666.944702</v>
+        <v>-7981740442.837309</v>
       </c>
       <c r="D7">
-        <v>-6751259904.6073475</v>
-      </c>
-      <c r="F7">
-        <v>-5507463077.742694</v>
+        <v>-7587401766.837309</v>
+      </c>
+      <c r="E7">
+        <v>-7224752865.998718</v>
       </c>
       <c r="H7">
-        <v>-6944724622.030547</v>
-      </c>
-      <c r="I7">
-        <v>-6753154970.781933</v>
+        <v>-5893723574.195272</v>
+      </c>
+      <c r="J7">
+        <v>-7431786040.757554</v>
+      </c>
+      <c r="K7">
+        <v>-7226780840.772249</v>
       </c>
     </row>
     <row r="8">
@@ -3165,22 +3682,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1001745804.2391579</v>
+        <v>1242818084.7383142</v>
       </c>
       <c r="C8">
-        <v>940579001.2391579</v>
+        <v>1072002673.7383143</v>
       </c>
       <c r="D8">
-        <v>756077531.9749582</v>
-      </c>
-      <c r="F8">
-        <v>915238454.9501661</v>
+        <v>1006545582.7383143</v>
+      </c>
+      <c r="E8">
+        <v>809104284.7166189</v>
       </c>
       <c r="H8">
-        <v>939320547.1803446</v>
-      </c>
-      <c r="I8">
-        <v>1557918453.7346237</v>
+        <v>979427802.2033913</v>
+      </c>
+      <c r="J8">
+        <v>1005198868.2440412</v>
+      </c>
+      <c r="K8">
+        <v>1667181529.469815</v>
       </c>
     </row>
     <row r="9">
@@ -3208,22 +3728,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>1001745804.2391579</v>
+        <v>1242818084.7383142</v>
       </c>
       <c r="C13">
-        <v>940579001.2391579</v>
+        <v>1072002673.7383143</v>
       </c>
       <c r="D13">
-        <v>756077531.9749582</v>
-      </c>
-      <c r="F13">
-        <v>915238454.9501661</v>
+        <v>1006545582.7383143</v>
+      </c>
+      <c r="E13">
+        <v>809104284.7166189</v>
       </c>
       <c r="H13">
-        <v>939320547.1803446</v>
-      </c>
-      <c r="I13">
-        <v>1557918453.7346237</v>
+        <v>979427802.2033913</v>
+      </c>
+      <c r="J13">
+        <v>1005198868.2440412</v>
+      </c>
+      <c r="K13">
+        <v>1667181529.469815</v>
       </c>
     </row>
     <row r="14"/>
@@ -3232,22 +3755,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-226140637.3214177</v>
+        <v>-261164059.36677513</v>
       </c>
       <c r="C15">
-        <v>-213396910.3214177</v>
+        <v>-242000874.36677513</v>
       </c>
       <c r="D15">
-        <v>-185233921.81217435</v>
-      </c>
-      <c r="F15">
-        <v>-126732254.66791885</v>
+        <v>-228363292.36677513</v>
+      </c>
+      <c r="E15">
+        <v>-198225120.40743643</v>
       </c>
       <c r="H15">
-        <v>-88732582.34292978</v>
-      </c>
-      <c r="I15">
-        <v>-80004285.1161908</v>
+        <v>-135620496.4797275</v>
+      </c>
+      <c r="J15">
+        <v>-94955754.57731305</v>
+      </c>
+      <c r="K15">
+        <v>-85615306.82457043</v>
       </c>
     </row>
     <row r="16">
@@ -3255,22 +3781,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-222092397.07651392</v>
+        <v>-268368599.9044387</v>
       </c>
       <c r="C16">
-        <v>-211461598.07651392</v>
+        <v>-237668700.9044387</v>
       </c>
       <c r="D16">
-        <v>-206385251.22616714</v>
-      </c>
-      <c r="F16">
-        <v>-173606708.99655935</v>
+        <v>-226292248.9044387</v>
+      </c>
+      <c r="E16">
+        <v>-220859877.46946886</v>
       </c>
       <c r="H16">
-        <v>-310182025.34436125</v>
-      </c>
-      <c r="I16">
-        <v>-962505360.4621854</v>
+        <v>-185782444.4772943</v>
+      </c>
+      <c r="J16">
+        <v>-331936336.06945205</v>
+      </c>
+      <c r="K16">
+        <v>-1030009725.5614009</v>
       </c>
     </row>
     <row r="17">
@@ -3283,22 +3812,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>239685404.65409932</v>
+        <v>238079515.45800787</v>
       </c>
       <c r="C18">
-        <v>259302734.65409932</v>
+        <v>256495371.45800787</v>
       </c>
       <c r="D18">
-        <v>261167326.32916808</v>
-      </c>
-      <c r="F18">
-        <v>159612225.93152848</v>
+        <v>277488676.4580079</v>
+      </c>
+      <c r="E18">
+        <v>279484039.4330249</v>
       </c>
       <c r="H18">
-        <v>386586748.5269154</v>
-      </c>
-      <c r="I18">
-        <v>482070834.4692714</v>
+        <v>170806472.13126555</v>
+      </c>
+      <c r="J18">
+        <v>413699629.2308195</v>
+      </c>
+      <c r="K18">
+        <v>515880397.46024626</v>
       </c>
     </row>
     <row r="19">
@@ -3306,22 +3838,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-166247948.26824555</v>
+        <v>-251127148.7230746</v>
       </c>
       <c r="C19">
-        <v>-128411406.26824555</v>
+        <v>-177907839.7230746</v>
       </c>
       <c r="D19">
-        <v>-144393167.88811934</v>
-      </c>
-      <c r="F19">
-        <v>-138062261.63386807</v>
+        <v>-137417413.7230746</v>
+      </c>
+      <c r="E19">
+        <v>-154520040.44732404</v>
       </c>
       <c r="H19">
-        <v>-63077947.19345335</v>
-      </c>
-      <c r="I19">
-        <v>-236124805.4566794</v>
+        <v>-147745122.32077456</v>
+      </c>
+      <c r="J19">
+        <v>-67501856.86914726</v>
+      </c>
+      <c r="K19">
+        <v>-252685186.033547</v>
       </c>
     </row>
     <row r="20">
@@ -3334,22 +3869,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>626950226.2270801</v>
+        <v>700237792.2020338</v>
       </c>
       <c r="C21">
-        <v>646611821.2270801</v>
+        <v>670920630.2020338</v>
       </c>
       <c r="D21">
-        <v>481232517.3776653</v>
-      </c>
-      <c r="F21">
-        <v>636449455.5833483</v>
+        <v>691961304.2020338</v>
+      </c>
+      <c r="E21">
+        <v>514983285.8254144</v>
       </c>
       <c r="H21">
-        <v>863914740.8265156</v>
-      </c>
-      <c r="I21">
-        <v>761354837.1688396</v>
+        <v>681086211.0568604</v>
+      </c>
+      <c r="J21">
+        <v>924504549.9589484</v>
+      </c>
+      <c r="K21">
+        <v>814751708.510543</v>
       </c>
     </row>
     <row r="22"/>
@@ -3368,22 +3906,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>13166123.254147137</v>
+        <v>33846619.63996107</v>
       </c>
       <c r="C25">
-        <v>5645112.254147137</v>
+        <v>14090230.63996107</v>
       </c>
       <c r="D25">
-        <v>5093476.553040396</v>
-      </c>
-      <c r="F25">
-        <v>8117593.317908744</v>
+        <v>6041026.639961069</v>
+      </c>
+      <c r="E25">
+        <v>5450702.512484018</v>
       </c>
       <c r="H25">
-        <v>137215328.65431422</v>
-      </c>
-      <c r="I25">
-        <v>22764886.571836706</v>
+        <v>8686912.726993317</v>
+      </c>
+      <c r="J25">
+        <v>146838790.531183</v>
+      </c>
+      <c r="K25">
+        <v>24361479.46130339</v>
       </c>
     </row>
     <row r="26">
@@ -3391,16 +3932,19 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-3809768.8118314</v>
+        <v>-4565052.455497785</v>
       </c>
       <c r="C26">
-        <v>-101457.81183139957</v>
-      </c>
-      <c r="F26">
-        <v>-48833.42894870897</v>
+        <v>-4077651.4554977845</v>
+      </c>
+      <c r="D26">
+        <v>-108573.45549778451</v>
       </c>
       <c r="H26">
-        <v>-3628732.2668729695</v>
+        <v>-52258.31337243552</v>
+      </c>
+      <c r="J26">
+        <v>-3883229.8290191917</v>
       </c>
     </row>
     <row r="27">
@@ -3438,22 +3982,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>636306580.6693958</v>
+        <v>729519359.386497</v>
       </c>
       <c r="C33">
-        <v>652155475.6693958</v>
+        <v>680933209.386497</v>
       </c>
       <c r="D33">
-        <v>486188931.78461325</v>
-      </c>
-      <c r="F33">
-        <v>644518215.4723083</v>
+        <v>697893757.386497</v>
+      </c>
+      <c r="E33">
+        <v>520287313.47323716</v>
       </c>
       <c r="H33">
-        <v>997501337.213957</v>
-      </c>
-      <c r="I33">
-        <v>784119723.7406763</v>
+        <v>689720865.4704813</v>
+      </c>
+      <c r="J33">
+        <v>1067460110.6611123</v>
+      </c>
+      <c r="K33">
+        <v>839113187.9718463</v>
       </c>
     </row>
     <row r="34"/>
@@ -3462,22 +4009,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>65656530.084784016</v>
+        <v>76429276.66372974</v>
       </c>
       <c r="C35">
-        <v>45908046.084784016</v>
+        <v>70261419.66372974</v>
       </c>
       <c r="D35">
-        <v>47561750.78825812</v>
-      </c>
-      <c r="F35">
-        <v>89767532.19107707</v>
+        <v>49127761.66372974</v>
+      </c>
+      <c r="E35">
+        <v>50897447.317186296</v>
       </c>
       <c r="H35">
-        <v>129333877.13791792</v>
-      </c>
-      <c r="I35">
-        <v>131047815.08034521</v>
+        <v>96063289.61332378</v>
+      </c>
+      <c r="J35">
+        <v>138404581.17828062</v>
+      </c>
+      <c r="K35">
+        <v>140238724.4695565</v>
       </c>
     </row>
     <row r="36">
@@ -3485,22 +4035,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-892085196.4013951</v>
+        <v>-880893678.1662784</v>
       </c>
       <c r="C36">
-        <v>-901103737.4013951</v>
+        <v>-954650652.1662784</v>
       </c>
       <c r="D36">
-        <v>-1099420175.269144</v>
-      </c>
-      <c r="F36">
-        <v>-870880375.3196902</v>
+        <v>-964301760.1662784</v>
+      </c>
+      <c r="E36">
+        <v>-1176526926.0026405</v>
       </c>
       <c r="H36">
-        <v>-642990413.2022974</v>
-      </c>
-      <c r="I36">
-        <v>-622805599.0828279</v>
+        <v>-931958712.3640603</v>
+      </c>
+      <c r="J36">
+        <v>-688085912.2936072</v>
+      </c>
+      <c r="K36">
+        <v>-666485456.1239717</v>
       </c>
     </row>
     <row r="37">
@@ -3508,22 +4061,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>471264468.7191757</v>
+        <v>500091866.548754</v>
       </c>
       <c r="C37">
-        <v>510034267.7191757</v>
+        <v>504315875.548754</v>
       </c>
       <c r="D37">
-        <v>703907525.2531389</v>
-      </c>
-      <c r="F37">
-        <v>479448215.3358718</v>
+        <v>545805018.548754</v>
+      </c>
+      <c r="E37">
+        <v>753275385.9764869</v>
       </c>
       <c r="H37">
-        <v>96470931.33800583</v>
-      </c>
-      <c r="I37">
-        <v>90803399.2508657</v>
+        <v>513073843.51799303</v>
+      </c>
+      <c r="J37">
+        <v>103236825.05456133</v>
+      </c>
+      <c r="K37">
+        <v>97171806.18871059</v>
       </c>
     </row>
     <row r="38">
@@ -3531,22 +4087,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>281142383.07196057</v>
+        <v>425146824.4327025</v>
       </c>
       <c r="C38">
-        <v>306994052.07196057</v>
+        <v>300859852.4327025</v>
       </c>
       <c r="D38">
-        <v>138238032.55686635</v>
-      </c>
-      <c r="F38">
-        <v>342853587.679567</v>
+        <v>328524777.4327025</v>
+      </c>
+      <c r="E38">
+        <v>147933220.76427025</v>
       </c>
       <c r="H38">
-        <v>580315732.4875833</v>
-      </c>
-      <c r="I38">
-        <v>383165338.9890592</v>
+        <v>366899286.23773795</v>
+      </c>
+      <c r="J38">
+        <v>621015604.600347</v>
+      </c>
+      <c r="K38">
+        <v>410038262.5061416</v>
       </c>
     </row>
     <row r="39"/>
@@ -3555,13 +4114,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-199183561.83663595</v>
+        <v>-297818319.14028126</v>
       </c>
       <c r="C40">
-        <v>-230811359.83663595</v>
-      </c>
-      <c r="F40">
-        <v>-302087470.464411</v>
+        <v>-213152891.14028126</v>
+      </c>
+      <c r="D40">
+        <v>-246999087.14028126</v>
+      </c>
+      <c r="H40">
+        <v>-323274077.55856365</v>
       </c>
     </row>
     <row r="41">
@@ -3569,19 +4131,22 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-6922065.100308207</v>
+        <v>-19947953.31580565</v>
       </c>
       <c r="C41">
-        <v>-6922065.100308207</v>
-      </c>
-      <c r="F41">
-        <v>-4829336.381903713</v>
+        <v>-7407537.315805651</v>
+      </c>
+      <c r="D41">
+        <v>-7407537.315805651</v>
       </c>
       <c r="H41">
-        <v>-65745888.930072874</v>
-      </c>
-      <c r="I41">
-        <v>-32606540.38515452</v>
+        <v>-5168037.130702047</v>
+      </c>
+      <c r="J41">
+        <v>-70356912.07074085</v>
+      </c>
+      <c r="K41">
+        <v>-34893367.967834</v>
       </c>
     </row>
     <row r="42">
@@ -3589,22 +4154,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-192261496.73632774</v>
+        <v>-277870365.8244756</v>
       </c>
       <c r="C42">
-        <v>-223889294.73632774</v>
+        <v>-205745353.8244756</v>
       </c>
       <c r="D42">
-        <v>109999144.12480319</v>
-      </c>
-      <c r="F42">
-        <v>-297258134.0825073</v>
+        <v>-239591549.8244756</v>
+      </c>
+      <c r="E42">
+        <v>117713825.71580884</v>
       </c>
       <c r="H42">
-        <v>-356274104.26018494</v>
-      </c>
-      <c r="I42">
-        <v>-226824798.6368755</v>
+        <v>-318106040.42786163</v>
+      </c>
+      <c r="J42">
+        <v>-381261037.5254988</v>
+      </c>
+      <c r="K42">
+        <v>-242732932.39873546</v>
       </c>
     </row>
     <row r="43">
@@ -3612,22 +4180,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>81958821.23532459</v>
+        <v>127328505.29242119</v>
       </c>
       <c r="C43">
-        <v>76182692.23532459</v>
+        <v>87706961.29242119</v>
       </c>
       <c r="D43">
-        <v>-163849437.90754467</v>
-      </c>
-      <c r="F43">
-        <v>40766117.21515594</v>
+        <v>81525690.29242119</v>
+      </c>
+      <c r="E43">
+        <v>-175340856.7942934</v>
       </c>
       <c r="H43">
-        <v>580315732.4875833</v>
-      </c>
-      <c r="I43">
-        <v>383165338.9890592</v>
+        <v>43625208.679174244</v>
+      </c>
+      <c r="J43">
+        <v>621015604.600347</v>
+      </c>
+      <c r="K43">
+        <v>410038262.5061416</v>
       </c>
     </row>
     <row r="44">
@@ -3641,22 +4212,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>81958821.23532459</v>
+        <v>127328505.29242119</v>
       </c>
       <c r="C46">
-        <v>76182692.23532459</v>
+        <v>87706961.29242119</v>
       </c>
       <c r="D46">
-        <v>-2955892.2213050053</v>
-      </c>
-      <c r="F46">
-        <v>40766117.21515594</v>
+        <v>81525690.29242119</v>
+      </c>
+      <c r="E46">
+        <v>-3163200.809804797</v>
       </c>
       <c r="H46">
-        <v>246444766.8386503</v>
-      </c>
-      <c r="I46">
-        <v>123733999.96702918</v>
+        <v>43625208.679174244</v>
+      </c>
+      <c r="J46">
+        <v>263728927.7387816</v>
+      </c>
+      <c r="K46">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="47">
@@ -3664,13 +4238,16 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>2166459.156519741</v>
+        <v>23236432.669390157</v>
       </c>
       <c r="C47">
-        <v>-95927596.84348026</v>
-      </c>
-      <c r="F47">
-        <v>-32790187.829219636</v>
+        <v>2319064.669390157</v>
+      </c>
+      <c r="D47">
+        <v>-102655384.33060984</v>
+      </c>
+      <c r="H47">
+        <v>-35089895.34444075</v>
       </c>
     </row>
     <row r="48">
@@ -3678,22 +4255,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>79792362.07880485</v>
+        <v>104092072.62303105</v>
       </c>
       <c r="C48">
-        <v>172110289.07880485</v>
+        <v>85387896.62303105</v>
       </c>
       <c r="D48">
-        <v>29834295.607914627</v>
-      </c>
-      <c r="F48">
-        <v>73556305.04437557</v>
+        <v>184181074.62303105</v>
+      </c>
+      <c r="E48">
+        <v>31926694.534635946</v>
       </c>
       <c r="H48">
-        <v>246444766.8386503</v>
-      </c>
-      <c r="I48">
-        <v>123733999.96702918</v>
+        <v>78715104.02361499</v>
+      </c>
+      <c r="J48">
+        <v>263728927.7387816</v>
+      </c>
+      <c r="K48">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="49"/>
@@ -3702,34 +4282,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>168653228.04255706</v>
+        <v>190263591.53146532</v>
       </c>
       <c r="C50">
-        <v>157803778.04255706</v>
+        <v>180481556.01724923</v>
       </c>
       <c r="D50">
-        <v>115383200.77639662</v>
-      </c>
-      <c r="F50">
-        <v>129514790.64617644</v>
+        <v>168871190.53146532</v>
+      </c>
+      <c r="E50">
+        <v>123475487.87574932</v>
       </c>
       <c r="H50">
-        <v>83094054.07858114</v>
-      </c>
-      <c r="I50">
-        <v>50911249.47339942</v>
+        <v>138598182.87718672</v>
+      </c>
+      <c r="J50">
+        <v>88921773.68878779</v>
+      </c>
+      <c r="K50">
+        <v>54481859.792348</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3740,6 +4323,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3747,27 +4332,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3781,28 +4372,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-1212593630</v>
+        <v>384674482</v>
       </c>
       <c r="C3">
-        <v>-537353405.8519752</v>
+        <v>-1297637689.4712086</v>
       </c>
       <c r="D3">
-        <v>1688979246.2945337</v>
+        <v>-575040157.516943</v>
       </c>
       <c r="E3">
-        <v>700557346</v>
+        <v>1807434141.5816789</v>
       </c>
       <c r="F3">
-        <v>-37817229.33641825</v>
+        <v>477297471</v>
       </c>
       <c r="G3">
-        <v>294880110.4972648</v>
+        <v>749690245.2023618</v>
       </c>
       <c r="H3">
-        <v>597895049.7322836</v>
+        <v>-40469503.45460134</v>
       </c>
       <c r="I3">
-        <v>586201404.7409139</v>
+        <v>315561236.5015354</v>
+      </c>
+      <c r="J3">
+        <v>639827829.9390982</v>
+      </c>
+      <c r="K3">
+        <v>627314062.6780105</v>
       </c>
     </row>
     <row r="4">
@@ -3810,28 +4407,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>13511423</v>
+        <v>84465857</v>
       </c>
       <c r="C4">
-        <v>76182692.23532459</v>
+        <v>14459033.339296153</v>
       </c>
       <c r="D4">
-        <v>52060253.075344056</v>
+        <v>81525690.29242119</v>
       </c>
       <c r="E4">
-        <v>7735294</v>
+        <v>55711447.62980145</v>
       </c>
       <c r="F4">
-        <v>40766117.21515594</v>
+        <v>38663042</v>
       </c>
       <c r="G4">
-        <v>95782262.511805</v>
+        <v>8277801.223102666</v>
       </c>
       <c r="H4">
-        <v>246444766.8386503</v>
+        <v>43625208.679174244</v>
       </c>
       <c r="I4">
-        <v>123733999.96702918</v>
+        <v>102499857.1187805</v>
+      </c>
+      <c r="J4">
+        <v>263728927.7387816</v>
+      </c>
+      <c r="K4">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="5">
@@ -3839,16 +4442,22 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>449218288</v>
+        <v>758762137</v>
       </c>
       <c r="C5">
-        <v>1032728249.4831454</v>
-      </c>
-      <c r="E5">
-        <v>198327843</v>
+        <v>480723770.0139757</v>
+      </c>
+      <c r="D5">
+        <v>1105157627.7132137</v>
       </c>
       <c r="F5">
-        <v>1220024395.7513738</v>
+        <v>378352910</v>
+      </c>
+      <c r="G5">
+        <v>212237370.85632604</v>
+      </c>
+      <c r="H5">
+        <v>1305589604.6570194</v>
       </c>
     </row>
     <row r="6">
@@ -3856,28 +4465,34 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>48518198</v>
+        <v>105403359</v>
       </c>
       <c r="C6">
-        <v>157803778.04255706</v>
+        <v>51920974.01173599</v>
       </c>
       <c r="D6">
-        <v>78272145.85962306</v>
+        <v>168871190.53146532</v>
       </c>
       <c r="E6">
-        <v>37668748</v>
+        <v>83761685.6879206</v>
       </c>
       <c r="F6">
-        <v>129514790.64617644</v>
+        <v>84010958</v>
       </c>
       <c r="G6">
-        <v>92403735.72940288</v>
+        <v>40310608.5259521</v>
       </c>
       <c r="H6">
-        <v>83094054.07858114</v>
+        <v>138598182.87718672</v>
       </c>
       <c r="I6">
-        <v>50911249.47339942</v>
+        <v>98884380.689358</v>
+      </c>
+      <c r="J6">
+        <v>88921773.68878779</v>
+      </c>
+      <c r="K6">
+        <v>54481859.792348</v>
       </c>
     </row>
     <row r="7">
@@ -3885,16 +4500,22 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>2129007</v>
+        <v>4383274</v>
       </c>
       <c r="C7">
-        <v>5593944.8300477825</v>
-      </c>
-      <c r="E7">
-        <v>9028576</v>
+        <v>2278322.8082338097</v>
+      </c>
+      <c r="D7">
+        <v>5986270.638987784</v>
       </c>
       <c r="F7">
-        <v>-6464115.664239144</v>
+        <v>10157161</v>
+      </c>
+      <c r="G7">
+        <v>9661786.281901551</v>
+      </c>
+      <c r="H7">
+        <v>-6917470.0472555915</v>
       </c>
     </row>
     <row r="8">
@@ -3902,28 +4523,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-7856020</v>
+        <v>11188484</v>
       </c>
       <c r="C8">
-        <v>10386068.239764135</v>
+        <v>-8406994.222161304</v>
       </c>
       <c r="D8">
-        <v>9260084.505223894</v>
+        <v>11114484.902364062</v>
       </c>
       <c r="E8">
-        <v>-3527599</v>
+        <v>9909531.40803393</v>
       </c>
       <c r="F8">
-        <v>274273.5913849972</v>
+        <v>-3177106</v>
       </c>
       <c r="G8">
-        <v>-5353648.415179287</v>
+        <v>-3775003.6801207224</v>
       </c>
       <c r="H8">
-        <v>21914251.313439574</v>
+        <v>293509.49947493797</v>
       </c>
       <c r="I8">
-        <v>-23337180.673980314</v>
+        <v>-5729121.271826611</v>
+      </c>
+      <c r="J8">
+        <v>23451185.737189732</v>
+      </c>
+      <c r="K8">
+        <v>-24973910.846419305</v>
       </c>
     </row>
     <row r="9">
@@ -3946,28 +4573,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>178953920</v>
+        <v>343047305</v>
       </c>
       <c r="C12">
-        <v>537328698.0758708</v>
+        <v>191504676.85585275</v>
       </c>
       <c r="D12">
-        <v>619778075.1697543</v>
+        <v>575013716.885306</v>
       </c>
       <c r="E12">
-        <v>195973502</v>
+        <v>663245599.8042748</v>
       </c>
       <c r="F12">
-        <v>805193544.8329278</v>
+        <v>416003695</v>
       </c>
       <c r="G12">
-        <v>586684970.5945795</v>
+        <v>209717910.47002387</v>
       </c>
       <c r="H12">
-        <v>529752969.85327363</v>
+        <v>861665000.7423612</v>
       </c>
       <c r="I12">
-        <v>376206994.96673214</v>
+        <v>627831542.9463652</v>
+      </c>
+      <c r="J12">
+        <v>566906672.4281842</v>
+      </c>
+      <c r="K12">
+        <v>402591901.88186693</v>
       </c>
     </row>
     <row r="13">
@@ -3999,11 +4632,11 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="H18">
-        <v>12658615.507962057</v>
-      </c>
-      <c r="I18">
-        <v>106958706.53965585</v>
+      <c r="J18">
+        <v>13546415.03407559</v>
+      </c>
+      <c r="K18">
+        <v>114460150.03637126</v>
       </c>
     </row>
     <row r="19">
@@ -4016,45 +4649,51 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>223885153</v>
+        <v>146586320</v>
       </c>
       <c r="C20">
-        <v>223889294.73632774</v>
+        <v>239587117.61155137</v>
       </c>
       <c r="D20">
-        <v>115141947.32797974</v>
+        <v>239591549.8244756</v>
       </c>
       <c r="E20">
-        <v>118413975</v>
+        <v>123217314.35443482</v>
       </c>
       <c r="F20">
-        <v>297258134.0825073</v>
+        <v>108307504</v>
       </c>
       <c r="G20">
-        <v>522399225.53529024</v>
+        <v>126718822.46330243</v>
       </c>
       <c r="H20">
-        <v>356274103.111837</v>
+        <v>318106040.42786163</v>
       </c>
       <c r="I20">
-        <v>226824798.6368755</v>
+        <v>559037180.4981053</v>
+      </c>
+      <c r="J20">
+        <v>381261036.2966127</v>
+      </c>
+      <c r="K20">
+        <v>242732932.39873546</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="D21">
-        <v>25686595.968098313</v>
-      </c>
-      <c r="G21">
-        <v>59806053.69991268</v>
-      </c>
-      <c r="H21">
-        <v>9633673.08095699</v>
+      <c r="E21">
+        <v>27488100.067310724</v>
       </c>
       <c r="I21">
-        <v>-47535636.04960769</v>
+        <v>64000492.349234685</v>
+      </c>
+      <c r="J21">
+        <v>10309321.250429137</v>
+      </c>
+      <c r="K21">
+        <v>-50869501.04707148</v>
       </c>
     </row>
     <row r="22">
@@ -4092,16 +4731,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1653362314</v>
+        <v>-449650634</v>
       </c>
       <c r="C28">
-        <v>-1620306475.520227</v>
-      </c>
-      <c r="E28">
-        <v>474370415</v>
+        <v>-1769319250.8340414</v>
+      </c>
+      <c r="D28">
+        <v>-1733945073.6924162</v>
       </c>
       <c r="F28">
-        <v>-1254232711.7713404</v>
+        <v>35593760</v>
+      </c>
+      <c r="G28">
+        <v>507639916.65872294</v>
+      </c>
+      <c r="H28">
+        <v>-1342197087.2155828</v>
       </c>
     </row>
     <row r="29">
@@ -4119,28 +4764,34 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-465897272</v>
+        <v>124307890</v>
       </c>
       <c r="C31">
-        <v>-474165237.6701927</v>
+        <v>-498572518.1230081</v>
       </c>
       <c r="D31">
-        <v>502316328.43987626</v>
+        <v>-507420349.4190509</v>
       </c>
       <c r="E31">
-        <v>288232014</v>
+        <v>537545789.2025886</v>
       </c>
       <c r="F31">
-        <v>-1164030611.9117384</v>
+        <v>334179293</v>
       </c>
       <c r="G31">
-        <v>-82895124.62433106</v>
+        <v>308446882.30680627</v>
       </c>
       <c r="H31">
-        <v>897884232.3616395</v>
+        <v>-1245668751.9584818</v>
       </c>
       <c r="I31">
-        <v>482240916.2760437</v>
+        <v>-88708892.51326913</v>
+      </c>
+      <c r="J31">
+        <v>960856458.3127388</v>
+      </c>
+      <c r="K31">
+        <v>516062407.7869549</v>
       </c>
     </row>
     <row r="32">
@@ -4153,28 +4804,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-74558397</v>
+        <v>5479244</v>
       </c>
       <c r="C33">
-        <v>-74557737.5209783</v>
+        <v>-79787476.71118566</v>
       </c>
       <c r="D33">
-        <v>6338774.734029852</v>
+        <v>-79786770.98025256</v>
       </c>
       <c r="E33">
-        <v>-9947475</v>
+        <v>6783338.454404524</v>
       </c>
       <c r="F33">
-        <v>12558813.046515666</v>
+        <v>11471801</v>
       </c>
       <c r="G33">
-        <v>-11136724.970848355</v>
+        <v>-10645131.35787511</v>
       </c>
       <c r="H33">
-        <v>16098156.310737047</v>
+        <v>13439613.025331048</v>
       </c>
       <c r="I33">
-        <v>-17559107.470091056</v>
+        <v>-11917788.203660589</v>
+      </c>
+      <c r="J33">
+        <v>17227184.642072693</v>
+      </c>
+      <c r="K33">
+        <v>-18790598.17151241</v>
       </c>
     </row>
     <row r="34">
@@ -4197,28 +4854,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>841006863</v>
+        <v>-1015343711</v>
       </c>
       <c r="C37">
-        <v>837597453.7136605</v>
+        <v>899990050.6922085</v>
       </c>
       <c r="D37">
-        <v>-894653084.5481198</v>
+        <v>896341525.8448635</v>
       </c>
       <c r="E37">
-        <v>-189121752</v>
+        <v>-957398697.1309687</v>
       </c>
       <c r="F37">
-        <v>233602427.38698357</v>
+        <v>-611295284</v>
       </c>
       <c r="G37">
-        <v>322273259.38247573</v>
+        <v>-202385619.73480505</v>
       </c>
       <c r="H37">
-        <v>-827535620.3753839</v>
+        <v>249985903.46323287</v>
       </c>
       <c r="I37">
-        <v>317939554.0459845</v>
+        <v>344875576.8933334</v>
+      </c>
+      <c r="J37">
+        <v>-885574015.7393341</v>
+      </c>
+      <c r="K37">
+        <v>340237931.4030684</v>
       </c>
     </row>
     <row r="38">
@@ -4231,28 +4894,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-520531545</v>
+        <v>-122227903</v>
       </c>
       <c r="C39">
-        <v>-520508104.52057135</v>
+        <v>-557038512.0286987</v>
       </c>
       <c r="D39">
-        <v>329227763.3294409</v>
+        <v>-557013427.5743412</v>
       </c>
       <c r="E39">
-        <v>159306589</v>
+        <v>352317828.12234426</v>
       </c>
       <c r="F39">
-        <v>54861295.49954324</v>
+        <v>-67772649</v>
       </c>
       <c r="G39">
-        <v>-600821236.536989</v>
+        <v>170479399.65468848</v>
       </c>
       <c r="H39">
-        <v>-1163883146.397402</v>
+        <v>58708938.404553965</v>
       </c>
       <c r="I39">
-        <v>-494278984.1033018</v>
+        <v>-642959241.9721789</v>
+      </c>
+      <c r="J39">
+        <v>-1245510944.0955954</v>
+      </c>
+      <c r="K39">
+        <v>-528944753.6401661</v>
       </c>
     </row>
     <row r="40">
@@ -4260,28 +4929,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-1486261849</v>
+        <v>382067658</v>
       </c>
       <c r="C40">
-        <v>-1441550575.9689858</v>
+        <v>-1590499359.365401</v>
       </c>
       <c r="D40">
-        <v>506701471.72364146</v>
+        <v>-1542652305.2543864</v>
       </c>
       <c r="E40">
-        <v>367623747</v>
+        <v>542238480.1898777</v>
       </c>
       <c r="F40">
-        <v>-259331800.10148925</v>
+        <v>377699461</v>
       </c>
       <c r="G40">
-        <v>-330688644.4395733</v>
+        <v>393406676.27606463</v>
       </c>
       <c r="H40">
-        <v>14108013.139141487</v>
+        <v>-277519780.3819123</v>
       </c>
       <c r="I40">
-        <v>-139283922.36072487</v>
+        <v>-353881166.6897293</v>
+      </c>
+      <c r="J40">
+        <v>15097464.740025898</v>
+      </c>
+      <c r="K40">
+        <v>-149052463.0190068</v>
       </c>
     </row>
     <row r="41">
@@ -4304,28 +4979,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-25824841</v>
+        <v>10999881</v>
       </c>
       <c r="C44">
-        <v>-25825460.4667731</v>
+        <v>-27636040.778311968</v>
       </c>
       <c r="D44">
-        <v>14550108.705264283</v>
+        <v>-27636703.690776836</v>
       </c>
       <c r="E44">
-        <v>4791978</v>
+        <v>15570566.243081832</v>
       </c>
       <c r="F44">
-        <v>-259199691.1341057</v>
+        <v>3850497</v>
       </c>
       <c r="G44">
-        <v>-259457591.4032644</v>
+        <v>5128058.655492742</v>
       </c>
       <c r="H44">
-        <v>228889057.3299814</v>
+        <v>-277378406.0822683</v>
       </c>
       <c r="I44">
-        <v>-7511459.566271286</v>
+        <v>-277654393.93269527</v>
+      </c>
+      <c r="J44">
+        <v>244941965.84136766</v>
+      </c>
+      <c r="K44">
+        <v>-8038268.381908519</v>
       </c>
     </row>
     <row r="45">
@@ -4348,28 +5029,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>78704727</v>
+        <v>165066307</v>
       </c>
       <c r="C48">
-        <v>78703186.91361377</v>
+        <v>84224605.48035556</v>
       </c>
       <c r="D48">
-        <v>275719382.6956896</v>
+        <v>84222957.38152806</v>
       </c>
       <c r="E48">
-        <v>-146514686</v>
+        <v>295056689.9346672</v>
       </c>
       <c r="F48">
-        <v>127306855.44295037</v>
+        <v>-12539359</v>
       </c>
       <c r="G48">
-        <v>36736187.74569526</v>
+        <v>-156790349.14164907</v>
       </c>
       <c r="H48">
-        <v>54227401.4431727</v>
+        <v>136235396.31396157</v>
       </c>
       <c r="I48">
-        <v>79038878.22739828</v>
+        <v>39312644.077063575</v>
+      </c>
+      <c r="J48">
+        <v>58030586.813115865</v>
+      </c>
+      <c r="K48">
+        <v>84582192.07484812</v>
       </c>
     </row>
     <row r="49">
@@ -4377,16 +5064,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-1190632603</v>
+        <v>393577360</v>
       </c>
       <c r="C49">
-        <v>-511395533.80175704</v>
-      </c>
-      <c r="E49">
-        <v>680433552</v>
+        <v>-1274136447.4807694</v>
+      </c>
+      <c r="D49">
+        <v>-547261755.6867813</v>
       </c>
       <c r="F49">
-        <v>6557801.195189349</v>
+        <v>452609712</v>
+      </c>
+      <c r="G49">
+        <v>728155088.7381517</v>
+      </c>
+      <c r="H49">
+        <v>7017726.12061061</v>
       </c>
     </row>
     <row r="50">
@@ -4414,28 +5107,34 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-12339630</v>
+        <v>-5430934</v>
       </c>
       <c r="C54">
-        <v>-12339595.770725723</v>
+        <v>-13205057.791809123</v>
       </c>
       <c r="D54">
-        <v>7981673.578958309</v>
+        <v>-13205021.161898421</v>
       </c>
       <c r="E54">
-        <v>17458554</v>
+        <v>8541460.391073348</v>
       </c>
       <c r="F54">
-        <v>-43966604.48910745</v>
+        <v>15043856</v>
       </c>
       <c r="G54">
-        <v>-4815412.01491438</v>
+        <v>18682992.48287188</v>
       </c>
       <c r="H54">
-        <v>20489291.673819944</v>
+        <v>-47050158.97464335</v>
       </c>
       <c r="I54">
-        <v>7953313.979336069</v>
+        <v>-5153136.1919536</v>
+      </c>
+      <c r="J54">
+        <v>21926287.95725851</v>
+      </c>
+      <c r="K54">
+        <v>8511111.818874324</v>
       </c>
     </row>
     <row r="55">
@@ -4478,28 +5177,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-309872</v>
+        <v>-685091</v>
       </c>
       <c r="C62">
-        <v>-4306321.191347431</v>
+        <v>-331604.56740303204</v>
       </c>
       <c r="D62">
-        <v>-649154.1751236925</v>
+        <v>-4608340.785083114</v>
       </c>
       <c r="E62">
-        <v>-739851</v>
+        <v>-694681.963584203</v>
       </c>
       <c r="F62">
-        <v>-4204029.259608352</v>
+        <v>-746869</v>
       </c>
       <c r="G62">
-        <v>-4283144.727009224</v>
+        <v>-791739.7209096035</v>
       </c>
       <c r="H62">
-        <v>-4318523.0289675165</v>
+        <v>-4498874.709499783</v>
       </c>
       <c r="I62">
-        <v>-1349606.1990781713</v>
+        <v>-4583538.8622543225</v>
+      </c>
+      <c r="J62">
+        <v>-4621398.38656221</v>
+      </c>
+      <c r="K62">
+        <v>-1444259.5000831548</v>
       </c>
     </row>
     <row r="63">
@@ -4507,16 +5212,22 @@
         <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
       </c>
       <c r="B63">
-        <v>-9311525</v>
+        <v>-2786853</v>
       </c>
       <c r="C63">
-        <v>-9311955.08814498</v>
-      </c>
-      <c r="E63">
-        <v>3405091</v>
+        <v>-9964579.631226823</v>
+      </c>
+      <c r="D63">
+        <v>-9965039.883180086</v>
       </c>
       <c r="F63">
-        <v>3795603.2171082026</v>
+        <v>10390772</v>
+      </c>
+      <c r="G63">
+        <v>3643903.702247889</v>
+      </c>
+      <c r="H63">
+        <v>4061804.108931179</v>
       </c>
     </row>
     <row r="64">
@@ -4535,16 +5246,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>2038858460</v>
+        <v>-743756748</v>
       </c>
       <c r="C67">
-        <v>1915250882.0252542</v>
-      </c>
-      <c r="E67">
-        <v>-447389390</v>
+        <v>2181851789.2042913</v>
+      </c>
+      <c r="D67">
+        <v>2049575115.5388677</v>
       </c>
       <c r="F67">
-        <v>-530448809.95158046</v>
+        <v>-498840948</v>
+      </c>
+      <c r="G67">
+        <v>-478766604.0547594</v>
+      </c>
+      <c r="H67">
+        <v>-567651314.5861744</v>
       </c>
     </row>
     <row r="68">
@@ -4576,8 +5293,8 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="D73">
-        <v>-174031166.95837516</v>
+      <c r="E73">
+        <v>-186236671.3800435</v>
       </c>
     </row>
     <row r="74">
@@ -4605,16 +5322,22 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>2134784282</v>
+        <v>-743756748</v>
       </c>
       <c r="C78">
-        <v>2011178478.8687344</v>
-      </c>
-      <c r="E78">
-        <v>-358208065</v>
+        <v>2284505274.214522</v>
+      </c>
+      <c r="D78">
+        <v>2152230499.8694773</v>
       </c>
       <c r="F78">
-        <v>-497658622.1223608</v>
+        <v>-498840948</v>
+      </c>
+      <c r="G78">
+        <v>-383330634.69626874</v>
+      </c>
+      <c r="H78">
+        <v>-532561419.24173355</v>
       </c>
     </row>
     <row r="79">
@@ -4716,23 +5439,23 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B98">
-        <v>-95925822</v>
-      </c>
       <c r="C98">
-        <v>-95927596.84348026</v>
-      </c>
-      <c r="E98">
-        <v>-89181325</v>
-      </c>
-      <c r="F98">
-        <v>-32790187.829219636</v>
+        <v>-102653485.01023085</v>
+      </c>
+      <c r="D98">
+        <v>-102655384.33060984</v>
+      </c>
+      <c r="G98">
+        <v>-95435969.35849063</v>
       </c>
       <c r="H98">
-        <v>1527213059.5591793</v>
-      </c>
-      <c r="I98">
-        <v>35817402.63310386</v>
+        <v>-35089895.34444075</v>
+      </c>
+      <c r="J98">
+        <v>1634322642.7279093</v>
+      </c>
+      <c r="K98">
+        <v>38329420.87587981</v>
       </c>
     </row>
     <row r="99">
@@ -4746,28 +5469,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-778064139</v>
+        <v>752553106</v>
       </c>
       <c r="C101">
-        <v>-1181245582.4213302</v>
+        <v>-832632900.761952</v>
       </c>
       <c r="D101">
-        <v>-42479378.733917</v>
+        <v>-1264091077.4628487</v>
       </c>
       <c r="E101">
-        <v>-67138500</v>
+        <v>-45458628.10647656</v>
       </c>
       <c r="F101">
-        <v>-10425063.895659203</v>
+        <v>309831328</v>
       </c>
       <c r="G101">
-        <v>-59545554.42490838</v>
+        <v>-71847192.54591724</v>
       </c>
       <c r="H101">
-        <v>-81791967.66375823</v>
+        <v>-11156215.4801629</v>
       </c>
       <c r="I101">
-        <v>-37843803.741145514</v>
+        <v>-63721723.21424796</v>
+      </c>
+      <c r="J101">
+        <v>-87528366.72620739</v>
+      </c>
+      <c r="K101">
+        <v>-40497941.629020385</v>
       </c>
     </row>
     <row r="102">
@@ -4784,6 +5513,12 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B104">
+        <v>1221420794</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4794,17 +5529,17 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="D106">
-        <v>-1507189296.6386337</v>
-      </c>
-      <c r="G106">
-        <v>-162762675.9566289</v>
-      </c>
-      <c r="H106">
-        <v>1127680721.0885715</v>
+      <c r="E106">
+        <v>-1612894532.9243503</v>
       </c>
       <c r="I106">
-        <v>-429929906.5092391</v>
+        <v>-174177875.8647371</v>
+      </c>
+      <c r="J106">
+        <v>1206769497.3579898</v>
+      </c>
+      <c r="K106">
+        <v>-460082616.89220786</v>
       </c>
     </row>
     <row r="107">
@@ -4821,39 +5556,45 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B109">
-        <v>-609994368</v>
-      </c>
       <c r="C109">
-        <v>-696680575.1565311</v>
+        <v>-652775721.9720592</v>
       </c>
       <c r="D109">
-        <v>548736020.675097</v>
+        <v>-745541580.8555696</v>
       </c>
       <c r="E109">
-        <v>121495745</v>
-      </c>
-      <c r="F109">
-        <v>758210692.3306383</v>
+        <v>587221080.8153908</v>
       </c>
       <c r="G109">
-        <v>515430169.7237959</v>
+        <v>130016729.3657836</v>
       </c>
       <c r="H109">
-        <v>-409799632.0247088</v>
+        <v>811387052.1720412</v>
       </c>
       <c r="I109">
-        <v>456067624.0579172</v>
+        <v>551579356.8238845</v>
+      </c>
+      <c r="J109">
+        <v>-438540525.44107014</v>
+      </c>
+      <c r="K109">
+        <v>488053477.5076621</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="C110">
-        <v>86622622.83276843</v>
+      <c r="B110">
+        <v>-240048709</v>
+      </c>
+      <c r="D110">
+        <v>92697815.13585022</v>
       </c>
       <c r="F110">
+        <v>722567310</v>
+      </c>
+      <c r="H110">
         <v>0</v>
       </c>
     </row>
@@ -4871,6 +5612,12 @@
       <c r="A113" t="str">
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
+      <c r="B113">
+        <v>110611950</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4897,28 +5644,34 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-168069771</v>
+        <v>-339430929</v>
       </c>
       <c r="C118">
-        <v>-571187630.0975677</v>
+        <v>-179857178.7898928</v>
       </c>
       <c r="D118">
-        <v>-590840456.9311123</v>
+        <v>-611247311.7431295</v>
       </c>
       <c r="E118">
-        <v>-188634245</v>
+        <v>-632278470.2227091</v>
       </c>
       <c r="F118">
-        <v>-768635756.2262975</v>
+        <v>-412735982</v>
       </c>
       <c r="G118">
-        <v>-574975724.1487043</v>
+        <v>-201863921.91170084</v>
       </c>
       <c r="H118">
-        <v>-533424751.38604546</v>
+        <v>-822543267.652204</v>
       </c>
       <c r="I118">
-        <v>-369144186.88471794</v>
+        <v>-615301080.0381324</v>
+      </c>
+      <c r="J118">
+        <v>-570835970.7409496</v>
+      </c>
+      <c r="K118">
+        <v>-395033750.71400744</v>
       </c>
     </row>
     <row r="119">
@@ -4945,14 +5698,14 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="D123">
-        <v>-374942.4779016518</v>
-      </c>
-      <c r="H123">
-        <v>124767240.91434476</v>
-      </c>
-      <c r="I123">
-        <v>-124767240.91434476</v>
+      <c r="E123">
+        <v>-401238.69915835623</v>
+      </c>
+      <c r="J123">
+        <v>133517668.42267509</v>
+      </c>
+      <c r="K123">
+        <v>-133517668.42267509</v>
       </c>
     </row>
     <row r="124">
@@ -4965,16 +5718,22 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>48200691</v>
+        <v>393470840</v>
       </c>
       <c r="C125">
-        <v>196651893.7519487</v>
-      </c>
-      <c r="E125">
-        <v>186029456</v>
+        <v>51581198.97113073</v>
+      </c>
+      <c r="D125">
+        <v>210443880.55907592</v>
       </c>
       <c r="F125">
-        <v>-578691103.1836579</v>
+        <v>288287851</v>
+      </c>
+      <c r="G125">
+        <v>199076448.60168517</v>
+      </c>
+      <c r="H125">
+        <v>-619277033.5209385</v>
       </c>
     </row>
     <row r="126">
@@ -4987,28 +5746,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>48200691</v>
+        <v>393470840</v>
       </c>
       <c r="C127">
-        <v>196651893.7519487</v>
+        <v>51581198.97113073</v>
       </c>
       <c r="D127">
-        <v>139310570.92198312</v>
+        <v>210443880.55907592</v>
       </c>
       <c r="E127">
-        <v>186029456</v>
+        <v>149080980.55085206</v>
       </c>
       <c r="F127">
-        <v>-578691103.1836579</v>
+        <v>288287851</v>
       </c>
       <c r="G127">
-        <v>72571880.11572751</v>
+        <v>199076448.60168517</v>
       </c>
       <c r="H127">
-        <v>907118628.3244456</v>
+        <v>-619277033.5209385</v>
       </c>
       <c r="I127">
-        <v>118427694.49052928</v>
+        <v>77661637.42255037</v>
+      </c>
+      <c r="J127">
+        <v>970738499.5377433</v>
+      </c>
+      <c r="K127">
+        <v>126733504.15678218</v>
       </c>
     </row>
     <row r="128">
@@ -5016,16 +5781,22 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>252714084</v>
+        <v>270439645</v>
       </c>
       <c r="C128">
-        <v>73389268.68138549</v>
-      </c>
-      <c r="E128">
-        <v>73389346</v>
+        <v>270437937.2820826</v>
+      </c>
+      <c r="D128">
+        <v>78536352.72988757</v>
       </c>
       <c r="F128">
-        <v>1035151476.7567383</v>
+        <v>78535396</v>
+      </c>
+      <c r="G128">
+        <v>78536435.47116694</v>
+      </c>
+      <c r="H128">
+        <v>1107750805.6440337</v>
       </c>
     </row>
     <row r="129">
@@ -5033,28 +5804,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>241265518</v>
+        <v>623127053</v>
       </c>
       <c r="C129">
-        <v>252718758.82022387</v>
-      </c>
-      <c r="E129">
-        <v>252714084</v>
+        <v>258186437.38594788</v>
+      </c>
+      <c r="D129">
+        <v>270442939.9662168</v>
       </c>
       <c r="F129">
-        <v>73389268.68138549</v>
+        <v>355603634</v>
+      </c>
+      <c r="G129">
+        <v>270437937.2820826</v>
+      </c>
+      <c r="H129">
+        <v>78536352.72988757</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5065,6 +5842,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5072,27 +5851,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5106,16 +5891,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-1212593630</v>
+        <v>1682312171.4712086</v>
       </c>
       <c r="C3">
-        <v>-2226332652.146509</v>
+        <v>-1297637689.4712086</v>
+      </c>
+      <c r="D3">
+        <v>-2382474299.098622</v>
       </c>
       <c r="E3">
-        <v>700557346</v>
+        <v>1330136670.5816789</v>
       </c>
       <c r="F3">
-        <v>-332697339.8336831</v>
+        <v>-272392774.2023618</v>
+      </c>
+      <c r="G3">
+        <v>749690245.2023618</v>
+      </c>
+      <c r="H3">
+        <v>-356030739.95613676</v>
       </c>
     </row>
     <row r="4">
@@ -5123,16 +5917,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>13511423</v>
+        <v>70006823.66070385</v>
       </c>
       <c r="C4">
-        <v>24122439.159980536</v>
+        <v>14459033.339296153</v>
+      </c>
+      <c r="D4">
+        <v>25814242.66261974</v>
       </c>
       <c r="E4">
-        <v>7735294</v>
+        <v>17048405.629801452</v>
       </c>
       <c r="F4">
-        <v>-55016145.29664906</v>
+        <v>30385240.776897334</v>
+      </c>
+      <c r="G4">
+        <v>8277801.223102666</v>
+      </c>
+      <c r="H4">
+        <v>-58874648.43960625</v>
       </c>
     </row>
     <row r="5">
@@ -5140,10 +5943,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>449218288</v>
-      </c>
-      <c r="E5">
-        <v>198327843</v>
+        <v>278038366.9860243</v>
+      </c>
+      <c r="C5">
+        <v>480723770.0139757</v>
+      </c>
+      <c r="F5">
+        <v>166115539.14367396</v>
+      </c>
+      <c r="G5">
+        <v>212237370.85632604</v>
       </c>
     </row>
     <row r="6">
@@ -5151,16 +5960,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>48518198</v>
+        <v>53482384.98826401</v>
       </c>
       <c r="C6">
-        <v>79531632.182934</v>
+        <v>51920974.01173599</v>
+      </c>
+      <c r="D6">
+        <v>85109504.84354472</v>
       </c>
       <c r="E6">
-        <v>37668748</v>
+        <v>-249272.31207939982</v>
       </c>
       <c r="F6">
-        <v>37111054.91677356</v>
+        <v>43700349.4740479</v>
+      </c>
+      <c r="G6">
+        <v>40310608.5259521</v>
+      </c>
+      <c r="H6">
+        <v>39713802.18782872</v>
       </c>
     </row>
     <row r="7">
@@ -5168,10 +5986,16 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>2129007</v>
-      </c>
-      <c r="E7">
-        <v>9028576</v>
+        <v>2104951.1917661903</v>
+      </c>
+      <c r="C7">
+        <v>2278322.8082338097</v>
+      </c>
+      <c r="F7">
+        <v>495374.7180984486</v>
+      </c>
+      <c r="G7">
+        <v>9661786.281901551</v>
       </c>
     </row>
     <row r="8">
@@ -5179,16 +6003,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-7856020</v>
+        <v>19595478.222161304</v>
       </c>
       <c r="C8">
-        <v>1125983.7345402408</v>
+        <v>-8406994.222161304</v>
+      </c>
+      <c r="D8">
+        <v>1204953.4943301324</v>
       </c>
       <c r="E8">
-        <v>-3527599</v>
+        <v>13086637.40803393</v>
       </c>
       <c r="F8">
-        <v>5627922.006564285</v>
+        <v>597897.6801207224</v>
+      </c>
+      <c r="G8">
+        <v>-3775003.6801207224</v>
+      </c>
+      <c r="H8">
+        <v>6022630.771301549</v>
       </c>
     </row>
     <row r="9">
@@ -5211,16 +6044,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>178953920</v>
+        <v>151542628.14414725</v>
       </c>
       <c r="C12">
-        <v>-82449377.09388351</v>
+        <v>191504676.85585275</v>
+      </c>
+      <c r="D12">
+        <v>-88231882.9189688</v>
       </c>
       <c r="E12">
-        <v>195973502</v>
+        <v>247241904.8042748</v>
       </c>
       <c r="F12">
-        <v>218508574.23834836</v>
+        <v>206285784.52997613</v>
+      </c>
+      <c r="G12">
+        <v>209717910.47002387</v>
+      </c>
+      <c r="H12">
+        <v>233833457.79599595</v>
       </c>
     </row>
     <row r="13">
@@ -5263,16 +6105,25 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>223885153</v>
+        <v>-93000797.61155137</v>
       </c>
       <c r="C20">
-        <v>108747347.408348</v>
+        <v>239587117.61155137</v>
+      </c>
+      <c r="D20">
+        <v>116374235.47004077</v>
       </c>
       <c r="E20">
-        <v>118413975</v>
+        <v>14909810.354434818</v>
       </c>
       <c r="F20">
-        <v>-225141091.45278293</v>
+        <v>-18411318.463302433</v>
+      </c>
+      <c r="G20">
+        <v>126718822.46330243</v>
+      </c>
+      <c r="H20">
+        <v>-240931140.07024366</v>
       </c>
     </row>
     <row r="21">
@@ -5315,10 +6166,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1653362314</v>
-      </c>
-      <c r="E28">
-        <v>474370415</v>
+        <v>1319668616.8340414</v>
+      </c>
+      <c r="C28">
+        <v>-1769319250.8340414</v>
+      </c>
+      <c r="F28">
+        <v>-472046156.65872294</v>
+      </c>
+      <c r="G28">
+        <v>507639916.65872294</v>
       </c>
     </row>
     <row r="29">
@@ -5336,16 +6193,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-465897272</v>
+        <v>622880408.123008</v>
       </c>
       <c r="C31">
-        <v>-976481566.110069</v>
+        <v>-498572518.1230081</v>
+      </c>
+      <c r="D31">
+        <v>-1044966138.6216395</v>
       </c>
       <c r="E31">
-        <v>288232014</v>
+        <v>203366496.20258856</v>
       </c>
       <c r="F31">
-        <v>-1081135487.2874074</v>
+        <v>25732410.693193734</v>
+      </c>
+      <c r="G31">
+        <v>308446882.30680627</v>
+      </c>
+      <c r="H31">
+        <v>-1156959859.4452126</v>
       </c>
     </row>
     <row r="32">
@@ -5358,16 +6224,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-74558397</v>
+        <v>85266720.71118566</v>
       </c>
       <c r="C33">
-        <v>-80896512.25500816</v>
+        <v>-79787476.71118566</v>
+      </c>
+      <c r="D33">
+        <v>-86570109.43465708</v>
       </c>
       <c r="E33">
-        <v>-9947475</v>
+        <v>-4688462.545595476</v>
       </c>
       <c r="F33">
-        <v>23695538.01736402</v>
+        <v>22116932.35787511</v>
+      </c>
+      <c r="G33">
+        <v>-10645131.35787511</v>
+      </c>
+      <c r="H33">
+        <v>25357401.228991635</v>
       </c>
     </row>
     <row r="34">
@@ -5390,16 +6265,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>841006863</v>
+        <v>-1915333761.6922085</v>
       </c>
       <c r="C37">
-        <v>1732250538.2617803</v>
+        <v>899990050.6922085</v>
+      </c>
+      <c r="D37">
+        <v>1853740222.9758322</v>
       </c>
       <c r="E37">
-        <v>-189121752</v>
+        <v>-346103413.1309687</v>
       </c>
       <c r="F37">
-        <v>-88670831.99549216</v>
+        <v>-408909664.26519495</v>
+      </c>
+      <c r="G37">
+        <v>-202385619.73480505</v>
+      </c>
+      <c r="H37">
+        <v>-94889673.4301005</v>
       </c>
     </row>
     <row r="38">
@@ -5412,16 +6296,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-520531545</v>
+        <v>434810609.0286987</v>
       </c>
       <c r="C39">
-        <v>-849735867.8500123</v>
+        <v>-557038512.0286987</v>
+      </c>
+      <c r="D39">
+        <v>-909331255.6966854</v>
       </c>
       <c r="E39">
-        <v>159306589</v>
+        <v>420090477.12234426</v>
       </c>
       <c r="F39">
-        <v>655682532.0365322</v>
+        <v>-238252048.65468848</v>
+      </c>
+      <c r="G39">
+        <v>170479399.65468848</v>
+      </c>
+      <c r="H39">
+        <v>701668180.376733</v>
       </c>
     </row>
     <row r="40">
@@ -5429,16 +6322,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-1486261849</v>
+        <v>1972567017.365401</v>
       </c>
       <c r="C40">
-        <v>-1948252047.6926272</v>
+        <v>-1590499359.365401</v>
+      </c>
+      <c r="D40">
+        <v>-2084890785.4442642</v>
       </c>
       <c r="E40">
-        <v>367623747</v>
+        <v>164539019.18987775</v>
       </c>
       <c r="F40">
-        <v>71356844.33808404</v>
+        <v>-15707215.276064634</v>
+      </c>
+      <c r="G40">
+        <v>393406676.27606463</v>
+      </c>
+      <c r="H40">
+        <v>76361386.30781698</v>
       </c>
     </row>
     <row r="41">
@@ -5461,16 +6363,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-25824841</v>
+        <v>38635921.77831197</v>
       </c>
       <c r="C44">
-        <v>-40375569.172037385</v>
+        <v>-27636040.778311968</v>
+      </c>
+      <c r="D44">
+        <v>-43207269.93385867</v>
       </c>
       <c r="E44">
-        <v>4791978</v>
+        <v>11720069.243081832</v>
       </c>
       <c r="F44">
-        <v>257900.26915869117</v>
+        <v>-1277561.6554927416</v>
+      </c>
+      <c r="G44">
+        <v>5128058.655492742</v>
+      </c>
+      <c r="H44">
+        <v>275987.8504269719</v>
       </c>
     </row>
     <row r="45">
@@ -5493,16 +6404,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>78704727</v>
+        <v>80841701.51964444</v>
       </c>
       <c r="C48">
-        <v>-197016195.78207585</v>
+        <v>84224605.48035556</v>
+      </c>
+      <c r="D48">
+        <v>-210833732.55313915</v>
       </c>
       <c r="E48">
-        <v>-146514686</v>
+        <v>307596048.9346672</v>
       </c>
       <c r="F48">
-        <v>90570667.6972551</v>
+        <v>144250990.14164907</v>
+      </c>
+      <c r="G48">
+        <v>-156790349.14164907</v>
+      </c>
+      <c r="H48">
+        <v>96922752.23689799</v>
       </c>
     </row>
     <row r="49">
@@ -5510,10 +6430,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-1190632603</v>
-      </c>
-      <c r="E49">
-        <v>680433552</v>
+        <v>1667713807.4807694</v>
+      </c>
+      <c r="C49">
+        <v>-1274136447.4807694</v>
+      </c>
+      <c r="F49">
+        <v>-275545376.73815167</v>
+      </c>
+      <c r="G49">
+        <v>728155088.7381517</v>
       </c>
     </row>
     <row r="50">
@@ -5541,16 +6467,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-12339630</v>
+        <v>7774123.791809123</v>
       </c>
       <c r="C54">
-        <v>-20321269.349684034</v>
+        <v>-13205057.791809123</v>
+      </c>
+      <c r="D54">
+        <v>-21746481.55297177</v>
       </c>
       <c r="E54">
-        <v>17458554</v>
+        <v>-6502395.608926652</v>
       </c>
       <c r="F54">
-        <v>-39151192.474193074</v>
+        <v>-3639136.482871879</v>
+      </c>
+      <c r="G54">
+        <v>18682992.48287188</v>
+      </c>
+      <c r="H54">
+        <v>-41897022.78268975</v>
       </c>
     </row>
     <row r="55">
@@ -5593,16 +6528,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-309872</v>
+        <v>-353486.43259696796</v>
       </c>
       <c r="C62">
-        <v>-3657167.016223739</v>
+        <v>-331604.56740303204</v>
+      </c>
+      <c r="D62">
+        <v>-3913658.821498911</v>
       </c>
       <c r="E62">
-        <v>-739851</v>
+        <v>52187.03641579696</v>
       </c>
       <c r="F62">
-        <v>79115.46740087215</v>
+        <v>44870.72090960352</v>
+      </c>
+      <c r="G62">
+        <v>-791739.7209096035</v>
+      </c>
+      <c r="H62">
+        <v>84664.15275453962</v>
       </c>
     </row>
     <row r="63">
@@ -5610,10 +6554,16 @@
         <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
       </c>
       <c r="B63">
-        <v>-9311525</v>
-      </c>
-      <c r="E63">
-        <v>3405091</v>
+        <v>7177726.631226823</v>
+      </c>
+      <c r="C63">
+        <v>-9964579.631226823</v>
+      </c>
+      <c r="F63">
+        <v>6746868.297752111</v>
+      </c>
+      <c r="G63">
+        <v>3643903.702247889</v>
       </c>
     </row>
     <row r="64">
@@ -5632,10 +6582,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>2038858460</v>
-      </c>
-      <c r="E67">
-        <v>-447389390</v>
+        <v>-2925608537.2042913</v>
+      </c>
+      <c r="C67">
+        <v>2181851789.2042913</v>
+      </c>
+      <c r="F67">
+        <v>-20074343.945240617</v>
+      </c>
+      <c r="G67">
+        <v>-478766604.0547594</v>
       </c>
     </row>
     <row r="68">
@@ -5693,10 +6649,16 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>2134784282</v>
-      </c>
-      <c r="E78">
-        <v>-358208065</v>
+        <v>-3028262022.214522</v>
+      </c>
+      <c r="C78">
+        <v>2284505274.214522</v>
+      </c>
+      <c r="F78">
+        <v>-115510313.30373126</v>
+      </c>
+      <c r="G78">
+        <v>-383330634.69626874</v>
       </c>
     </row>
     <row r="79">
@@ -5798,11 +6760,11 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B98">
-        <v>-95925822</v>
-      </c>
-      <c r="E98">
-        <v>-89181325</v>
+      <c r="C98">
+        <v>-102653485.01023085</v>
+      </c>
+      <c r="G98">
+        <v>-95435969.35849063</v>
       </c>
     </row>
     <row r="99">
@@ -5816,16 +6778,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-778064139</v>
+        <v>1585186006.761952</v>
       </c>
       <c r="C101">
-        <v>-1138766203.6874132</v>
+        <v>-832632900.761952</v>
+      </c>
+      <c r="D101">
+        <v>-1218632449.356372</v>
       </c>
       <c r="E101">
-        <v>-67138500</v>
+        <v>-355289956.10647655</v>
       </c>
       <c r="F101">
-        <v>49120490.52924918</v>
+        <v>381678520.5459173</v>
+      </c>
+      <c r="G101">
+        <v>-71847192.54591724</v>
+      </c>
+      <c r="H101">
+        <v>52565507.73408505</v>
       </c>
     </row>
     <row r="102">
@@ -5867,17 +6838,17 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B109">
-        <v>-609994368</v>
-      </c>
       <c r="C109">
-        <v>-1245416595.831628</v>
-      </c>
-      <c r="E109">
-        <v>121495745</v>
-      </c>
-      <c r="F109">
-        <v>242780522.6068424</v>
+        <v>-652775721.9720592</v>
+      </c>
+      <c r="D109">
+        <v>-1332762661.6709604</v>
+      </c>
+      <c r="G109">
+        <v>130016729.3657836</v>
+      </c>
+      <c r="H109">
+        <v>259807695.3481567</v>
       </c>
     </row>
     <row r="110">
@@ -5925,16 +6896,25 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-168069771</v>
+        <v>-159573750.2101072</v>
       </c>
       <c r="C118">
-        <v>19652826.833544612</v>
+        <v>-179857178.7898928</v>
+      </c>
+      <c r="D118">
+        <v>21031158.479579568</v>
       </c>
       <c r="E118">
-        <v>-188634245</v>
+        <v>-219542488.22270906</v>
       </c>
       <c r="F118">
-        <v>-193660032.0775932</v>
+        <v>-210872060.08829916</v>
+      </c>
+      <c r="G118">
+        <v>-201863921.91170084</v>
+      </c>
+      <c r="H118">
+        <v>-207242187.6140716</v>
       </c>
     </row>
     <row r="119">
@@ -5972,10 +6952,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>48200691</v>
-      </c>
-      <c r="E125">
-        <v>186029456</v>
+        <v>341889641.0288693</v>
+      </c>
+      <c r="C125">
+        <v>51581198.97113073</v>
+      </c>
+      <c r="F125">
+        <v>89211402.39831483</v>
+      </c>
+      <c r="G125">
+        <v>199076448.60168517</v>
       </c>
     </row>
     <row r="126">
@@ -5988,16 +6974,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>48200691</v>
+        <v>341889641.0288693</v>
       </c>
       <c r="C127">
-        <v>57341322.82996559</v>
+        <v>51581198.97113073</v>
+      </c>
+      <c r="D127">
+        <v>61362900.00822386</v>
       </c>
       <c r="E127">
-        <v>186029456</v>
+        <v>-139206870.44914794</v>
       </c>
       <c r="F127">
-        <v>-651262983.2993854</v>
+        <v>89211402.39831483</v>
+      </c>
+      <c r="G127">
+        <v>199076448.60168517</v>
+      </c>
+      <c r="H127">
+        <v>-696938670.9434888</v>
       </c>
     </row>
     <row r="128">
@@ -6005,10 +7000,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>252714084</v>
-      </c>
-      <c r="E128">
-        <v>73389346</v>
+        <v>1707.7179173827171</v>
+      </c>
+      <c r="C128">
+        <v>270437937.2820826</v>
+      </c>
+      <c r="F128">
+        <v>-1039.4711669385433</v>
+      </c>
+      <c r="G128">
+        <v>78536435.47116694</v>
       </c>
     </row>
     <row r="129">
@@ -6016,22 +7017,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>241265518</v>
-      </c>
-      <c r="E129">
-        <v>252714084</v>
+        <v>364940615.6140521</v>
+      </c>
+      <c r="C129">
+        <v>258186437.38594788</v>
+      </c>
+      <c r="F129">
+        <v>85165696.71791738</v>
+      </c>
+      <c r="G129">
+        <v>270437937.2820826</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6042,6 +7049,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6049,27 +7058,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6083,22 +7098,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-2450504381.8519754</v>
+        <v>-667663146.516943</v>
       </c>
       <c r="C3">
-        <v>-537353405.8519752</v>
+        <v>-2622368092.1905136</v>
       </c>
       <c r="D3">
-        <v>1356281906.4608507</v>
-      </c>
-      <c r="F3">
-        <v>-37817229.33641825</v>
+        <v>-575040157.516943</v>
+      </c>
+      <c r="E3">
+        <v>1451403401.6255422</v>
       </c>
       <c r="H3">
-        <v>597895049.7322836</v>
-      </c>
-      <c r="I3">
-        <v>586201404.7409139</v>
+        <v>-40469503.45460134</v>
+      </c>
+      <c r="J3">
+        <v>639827829.9390982</v>
+      </c>
+      <c r="K3">
+        <v>627314062.6780105</v>
       </c>
     </row>
     <row r="4">
@@ -6106,22 +7124,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>81958821.23532459</v>
+        <v>127328505.29242119</v>
       </c>
       <c r="C4">
-        <v>76182692.23532459</v>
+        <v>87706922.40861468</v>
       </c>
       <c r="D4">
-        <v>-2955892.2213050053</v>
-      </c>
-      <c r="F4">
-        <v>40766117.21515594</v>
+        <v>81525690.29242119</v>
+      </c>
+      <c r="E4">
+        <v>-3163200.809804797</v>
       </c>
       <c r="H4">
-        <v>246444766.8386503</v>
-      </c>
-      <c r="I4">
-        <v>123733999.96702918</v>
+        <v>43625208.679174244</v>
+      </c>
+      <c r="J4">
+        <v>263728927.7387816</v>
+      </c>
+      <c r="K4">
+        <v>132411962.13957213</v>
       </c>
     </row>
     <row r="5">
@@ -6129,13 +7150,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>1283618694.4831452</v>
+        <v>1485566854.7132137</v>
       </c>
       <c r="C5">
-        <v>1032728249.4831454</v>
-      </c>
-      <c r="F5">
-        <v>1220024395.7513738</v>
+        <v>1373644026.8708632</v>
+      </c>
+      <c r="D5">
+        <v>1105157627.7132137</v>
+      </c>
+      <c r="H5">
+        <v>1305589604.6570194</v>
       </c>
     </row>
     <row r="6">
@@ -6143,22 +7167,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>168653228.04255706</v>
+        <v>190263591.53146532</v>
       </c>
       <c r="C6">
-        <v>157803778.04255706</v>
+        <v>180481556.01724923</v>
       </c>
       <c r="D6">
-        <v>115383200.77639662</v>
-      </c>
-      <c r="F6">
-        <v>129514790.64617644</v>
+        <v>168871190.53146532</v>
+      </c>
+      <c r="E6">
+        <v>123475487.87574932</v>
       </c>
       <c r="H6">
-        <v>83094054.07858114</v>
-      </c>
-      <c r="I6">
-        <v>50911249.47339942</v>
+        <v>138598182.87718672</v>
+      </c>
+      <c r="J6">
+        <v>88921773.68878779</v>
+      </c>
+      <c r="K6">
+        <v>54481859.792348</v>
       </c>
     </row>
     <row r="7">
@@ -6166,13 +7193,16 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-1305624.1699522175</v>
+        <v>212383.63898778427</v>
       </c>
       <c r="C7">
-        <v>5593944.8300477825</v>
-      </c>
-      <c r="F7">
-        <v>-6464115.664239144</v>
+        <v>-1397192.8346799575</v>
+      </c>
+      <c r="D7">
+        <v>5986270.638987784</v>
+      </c>
+      <c r="H7">
+        <v>-6917470.0472555915</v>
       </c>
     </row>
     <row r="8">
@@ -6180,22 +7210,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>6057647.239764135</v>
+        <v>25480074.90236406</v>
       </c>
       <c r="C8">
-        <v>10386068.239764135</v>
+        <v>6482494.360323481</v>
       </c>
       <c r="D8">
-        <v>14888006.511788178</v>
-      </c>
-      <c r="F8">
-        <v>274273.5913849972</v>
+        <v>11114484.902364062</v>
+      </c>
+      <c r="E8">
+        <v>15932162.179335479</v>
       </c>
       <c r="H8">
-        <v>21914251.313439574</v>
-      </c>
-      <c r="I8">
-        <v>-23337180.673980314</v>
+        <v>293509.49947493797</v>
+      </c>
+      <c r="J8">
+        <v>23451185.737189732</v>
+      </c>
+      <c r="K8">
+        <v>-24973910.846419305</v>
       </c>
     </row>
     <row r="9">
@@ -6218,22 +7251,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>520309116.07587075</v>
+        <v>502057326.885306</v>
       </c>
       <c r="C12">
-        <v>537328698.0758708</v>
+        <v>556800483.2711349</v>
       </c>
       <c r="D12">
-        <v>838286649.4081026</v>
-      </c>
-      <c r="F12">
-        <v>805193544.8329278</v>
+        <v>575013716.885306</v>
+      </c>
+      <c r="E12">
+        <v>897079057.6002707</v>
       </c>
       <c r="H12">
-        <v>529752969.85327363</v>
-      </c>
-      <c r="I12">
-        <v>376206994.96673214</v>
+        <v>861665000.7423612</v>
+      </c>
+      <c r="J12">
+        <v>566906672.4281842</v>
+      </c>
+      <c r="K12">
+        <v>402591901.88186693</v>
       </c>
     </row>
     <row r="13">
@@ -6265,11 +7301,11 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="H18">
-        <v>12658615.507962057</v>
-      </c>
-      <c r="I18">
-        <v>106958706.53965585</v>
+      <c r="J18">
+        <v>13546415.03407559</v>
+      </c>
+      <c r="K18">
+        <v>114460150.03637126</v>
       </c>
     </row>
     <row r="19">
@@ -6282,33 +7318,36 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>329360472.73632777</v>
+        <v>277870365.8244756</v>
       </c>
       <c r="C20">
-        <v>223889294.73632774</v>
+        <v>352459844.97272456</v>
       </c>
       <c r="D20">
-        <v>-109999144.12480319</v>
-      </c>
-      <c r="F20">
-        <v>297258134.0825073</v>
+        <v>239591549.8244756</v>
+      </c>
+      <c r="E20">
+        <v>-117713825.71580884</v>
       </c>
       <c r="H20">
-        <v>356274103.111837</v>
-      </c>
-      <c r="I20">
-        <v>226824798.6368755</v>
+        <v>318106040.42786163</v>
+      </c>
+      <c r="J20">
+        <v>381261036.2966127</v>
+      </c>
+      <c r="K20">
+        <v>242732932.39873546</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="H21">
-        <v>9633673.08095699</v>
-      </c>
-      <c r="I21">
-        <v>-47535636.04960769</v>
+      <c r="J21">
+        <v>10309321.250429137</v>
+      </c>
+      <c r="K21">
+        <v>-50869501.04707148</v>
       </c>
     </row>
     <row r="22">
@@ -6346,13 +7385,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-3748039204.520227</v>
+        <v>-2219189467.692416</v>
       </c>
       <c r="C28">
-        <v>-1620306475.520227</v>
-      </c>
-      <c r="F28">
-        <v>-1254232711.7713404</v>
+        <v>-4010904241.1851807</v>
+      </c>
+      <c r="D28">
+        <v>-1733945073.6924162</v>
+      </c>
+      <c r="H28">
+        <v>-1342197087.2155828</v>
       </c>
     </row>
     <row r="29">
@@ -6370,22 +7412,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-1228294523.6701927</v>
+        <v>-717291752.4190509</v>
       </c>
       <c r="C31">
-        <v>-474165237.6701927</v>
+        <v>-1314439749.8488653</v>
       </c>
       <c r="D31">
-        <v>-578819158.8475311</v>
-      </c>
-      <c r="F31">
-        <v>-1164030611.9117384</v>
+        <v>-507420349.4190509</v>
+      </c>
+      <c r="E31">
+        <v>-619414070.242624</v>
       </c>
       <c r="H31">
-        <v>897884232.3616395</v>
-      </c>
-      <c r="I31">
-        <v>482240916.2760437</v>
+        <v>-1245668751.9584818</v>
+      </c>
+      <c r="J31">
+        <v>960856458.3127388</v>
+      </c>
+      <c r="K31">
+        <v>516062407.7869549</v>
       </c>
     </row>
     <row r="32">
@@ -6398,22 +7443,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-139168659.5209783</v>
+        <v>-85779327.98025256</v>
       </c>
       <c r="C33">
-        <v>-74557737.5209783</v>
+        <v>-148929116.33356312</v>
       </c>
       <c r="D33">
-        <v>30034312.751393873</v>
-      </c>
-      <c r="F33">
-        <v>12558813.046515666</v>
+        <v>-79786770.98025256</v>
+      </c>
+      <c r="E33">
+        <v>32140739.68339616</v>
       </c>
       <c r="H33">
-        <v>16098156.310737047</v>
-      </c>
-      <c r="I33">
-        <v>-17559107.470091056</v>
+        <v>13439613.025331048</v>
+      </c>
+      <c r="J33">
+        <v>17227184.642072693</v>
+      </c>
+      <c r="K33">
+        <v>-18790598.17151241</v>
       </c>
     </row>
     <row r="34">
@@ -6436,22 +7484,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>1867726068.7136605</v>
+        <v>492293098.8448634</v>
       </c>
       <c r="C37">
-        <v>837597453.7136605</v>
+        <v>1998717196.271877</v>
       </c>
       <c r="D37">
-        <v>-983323916.543612</v>
-      </c>
-      <c r="F37">
-        <v>233602427.38698357</v>
+        <v>896341525.8448635</v>
+      </c>
+      <c r="E37">
+        <v>-1052288370.5610693</v>
       </c>
       <c r="H37">
-        <v>-827535620.3753839</v>
-      </c>
-      <c r="I37">
-        <v>317939554.0459845</v>
+        <v>249985903.46323287</v>
+      </c>
+      <c r="J37">
+        <v>-885574015.7393341</v>
+      </c>
+      <c r="K37">
+        <v>340237931.4030684</v>
       </c>
     </row>
     <row r="38">
@@ -6464,22 +7515,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-1200346238.5205712</v>
+        <v>-611468681.5743412</v>
       </c>
       <c r="C39">
-        <v>-520508104.52057135</v>
+        <v>-1284531339.2577283</v>
       </c>
       <c r="D39">
-        <v>984910295.365973</v>
-      </c>
-      <c r="F39">
-        <v>54861295.49954324</v>
+        <v>-557013427.5743412</v>
+      </c>
+      <c r="E39">
+        <v>1053986008.4990772</v>
       </c>
       <c r="H39">
-        <v>-1163883146.397402</v>
-      </c>
-      <c r="I39">
-        <v>-494278984.1033018</v>
+        <v>58708938.404553965</v>
+      </c>
+      <c r="J39">
+        <v>-1245510944.0955954</v>
+      </c>
+      <c r="K39">
+        <v>-528944753.6401661</v>
       </c>
     </row>
     <row r="40">
@@ -6487,22 +7541,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-3295436171.9689856</v>
+        <v>-1538284108.2543864</v>
       </c>
       <c r="C40">
-        <v>-1441550575.9689858</v>
+        <v>-3526558340.895852</v>
       </c>
       <c r="D40">
-        <v>578058316.0617255</v>
-      </c>
-      <c r="F40">
-        <v>-259331800.10148925</v>
+        <v>-1542652305.2543864</v>
+      </c>
+      <c r="E40">
+        <v>618599866.4976947</v>
       </c>
       <c r="H40">
-        <v>14108013.139141487</v>
-      </c>
-      <c r="I40">
-        <v>-139283922.36072487</v>
+        <v>-277519780.3819123</v>
+      </c>
+      <c r="J40">
+        <v>15097464.740025898</v>
+      </c>
+      <c r="K40">
+        <v>-149052463.0190068</v>
       </c>
     </row>
     <row r="41">
@@ -6525,22 +7582,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-56442279.4667731</v>
+        <v>-20487319.690776836</v>
       </c>
       <c r="C44">
-        <v>-25825460.4667731</v>
+        <v>-60400803.124581546</v>
       </c>
       <c r="D44">
-        <v>14808008.974422975</v>
-      </c>
-      <c r="F44">
-        <v>-259199691.1341057</v>
+        <v>-27636703.690776836</v>
+      </c>
+      <c r="E44">
+        <v>15846554.093508804</v>
       </c>
       <c r="H44">
-        <v>228889057.3299814</v>
-      </c>
-      <c r="I44">
-        <v>-7511459.566271286</v>
+        <v>-277378406.0822683</v>
+      </c>
+      <c r="J44">
+        <v>244941965.84136766</v>
+      </c>
+      <c r="K44">
+        <v>-8038268.381908519</v>
       </c>
     </row>
     <row r="45">
@@ -6563,22 +7623,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>303922599.9136138</v>
+        <v>261828623.38152808</v>
       </c>
       <c r="C48">
-        <v>78703186.91361377</v>
+        <v>325237912.0035327</v>
       </c>
       <c r="D48">
-        <v>366290050.3929447</v>
-      </c>
-      <c r="F48">
-        <v>127306855.44295037</v>
+        <v>84222957.38152806</v>
+      </c>
+      <c r="E48">
+        <v>391979442.17156523</v>
       </c>
       <c r="H48">
-        <v>54227401.4431727</v>
-      </c>
-      <c r="I48">
-        <v>79038878.22739828</v>
+        <v>136235396.31396157</v>
+      </c>
+      <c r="J48">
+        <v>58030586.813115865</v>
+      </c>
+      <c r="K48">
+        <v>84582192.07484812</v>
       </c>
     </row>
     <row r="49">
@@ -6586,13 +7649,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-2382461688.801757</v>
+        <v>-606294107.6867813</v>
       </c>
       <c r="C49">
-        <v>-511395533.80175704</v>
-      </c>
-      <c r="F49">
-        <v>6557801.195189349</v>
+        <v>-2549553291.9057026</v>
+      </c>
+      <c r="D49">
+        <v>-547261755.6867813</v>
+      </c>
+      <c r="H49">
+        <v>7017726.12061061</v>
       </c>
     </row>
     <row r="50">
@@ -6620,22 +7686,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-42137779.77072573</v>
+        <v>-33679811.16189842</v>
       </c>
       <c r="C54">
-        <v>-12339595.770725723</v>
+        <v>-45093071.43657942</v>
       </c>
       <c r="D54">
-        <v>-31169518.895234764</v>
-      </c>
-      <c r="F54">
-        <v>-43966604.48910745</v>
+        <v>-13205021.161898421</v>
+      </c>
+      <c r="E54">
+        <v>-33355562.391616404</v>
       </c>
       <c r="H54">
-        <v>20489291.673819944</v>
-      </c>
-      <c r="I54">
-        <v>7953313.979336069</v>
+        <v>-47050158.97464335</v>
+      </c>
+      <c r="J54">
+        <v>21926287.95725851</v>
+      </c>
+      <c r="K54">
+        <v>8511111.818874324</v>
       </c>
     </row>
     <row r="55">
@@ -6678,22 +7747,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-3876342.1913474314</v>
+        <v>-4546562.785083114</v>
       </c>
       <c r="C62">
-        <v>-4306321.191347431</v>
+        <v>-4148205.6315765427</v>
       </c>
       <c r="D62">
-        <v>-570038.7077228203</v>
-      </c>
-      <c r="F62">
-        <v>-4204029.259608352</v>
+        <v>-4608340.785083114</v>
+      </c>
+      <c r="E62">
+        <v>-610017.8108296634</v>
       </c>
       <c r="H62">
-        <v>-4318523.0289675165</v>
-      </c>
-      <c r="I62">
-        <v>-1349606.1990781713</v>
+        <v>-4498874.709499783</v>
+      </c>
+      <c r="J62">
+        <v>-4621398.38656221</v>
+      </c>
+      <c r="K62">
+        <v>-1444259.5000831548</v>
       </c>
     </row>
     <row r="63">
@@ -6701,13 +7773,16 @@
         <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
       </c>
       <c r="B63">
-        <v>-22028571.08814498</v>
+        <v>-23142664.883180086</v>
       </c>
       <c r="C63">
-        <v>-9311955.08814498</v>
-      </c>
-      <c r="F63">
-        <v>3795603.2171082026</v>
+        <v>-23573523.216654796</v>
+      </c>
+      <c r="D63">
+        <v>-9965039.883180086</v>
+      </c>
+      <c r="H63">
+        <v>4061804.108931179</v>
       </c>
     </row>
     <row r="64">
@@ -6726,13 +7801,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>4401498732.025254</v>
+        <v>1804659315.538868</v>
       </c>
       <c r="C67">
-        <v>1915250882.0252542</v>
-      </c>
-      <c r="F67">
-        <v>-530448809.95158046</v>
+        <v>4710193508.797918</v>
+      </c>
+      <c r="D67">
+        <v>2049575115.5388677</v>
+      </c>
+      <c r="H67">
+        <v>-567651314.5861744</v>
       </c>
     </row>
     <row r="68">
@@ -6790,13 +7868,16 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>4504170825.868734</v>
+        <v>1907314699.8694773</v>
       </c>
       <c r="C78">
-        <v>2011178478.8687344</v>
-      </c>
-      <c r="F78">
-        <v>-497658622.1223608</v>
+        <v>4820066408.780268</v>
+      </c>
+      <c r="D78">
+        <v>2152230499.8694773</v>
+      </c>
+      <c r="H78">
+        <v>-532561419.24173355</v>
       </c>
     </row>
     <row r="79">
@@ -6898,20 +7979,20 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B98">
-        <v>-102672093.84348026</v>
-      </c>
       <c r="C98">
-        <v>-95927596.84348026</v>
-      </c>
-      <c r="F98">
-        <v>-32790187.829219636</v>
+        <v>-109872899.98235007</v>
+      </c>
+      <c r="D98">
+        <v>-102655384.33060984</v>
       </c>
       <c r="H98">
-        <v>1527213059.5591793</v>
-      </c>
-      <c r="I98">
-        <v>35817402.63310386</v>
+        <v>-35089895.34444075</v>
+      </c>
+      <c r="J98">
+        <v>1634322642.7279093</v>
+      </c>
+      <c r="K98">
+        <v>38329420.87587981</v>
       </c>
     </row>
     <row r="99">
@@ -6925,22 +8006,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-1892171221.4213302</v>
+        <v>-821369299.4628487</v>
       </c>
       <c r="C101">
-        <v>-1181245582.4213302</v>
+        <v>-2024876785.6788836</v>
       </c>
       <c r="D101">
-        <v>6641111.7953321785</v>
-      </c>
-      <c r="F101">
-        <v>-10425063.895659203</v>
+        <v>-1264091077.4628487</v>
+      </c>
+      <c r="E101">
+        <v>7106879.627608493</v>
       </c>
       <c r="H101">
-        <v>-81791967.66375823</v>
-      </c>
-      <c r="I101">
-        <v>-37843803.741145514</v>
+        <v>-11156215.4801629</v>
+      </c>
+      <c r="J101">
+        <v>-87528366.72620739</v>
+      </c>
+      <c r="K101">
+        <v>-40497941.629020385</v>
       </c>
     </row>
     <row r="102">
@@ -6967,11 +8051,11 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="H106">
-        <v>1127680721.0885715</v>
-      </c>
-      <c r="I106">
-        <v>-429929906.5092391</v>
+      <c r="J106">
+        <v>1206769497.3579898</v>
+      </c>
+      <c r="K106">
+        <v>-460082616.89220786</v>
       </c>
     </row>
     <row r="107">
@@ -6988,33 +8072,36 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B109">
-        <v>-1428170688.156531</v>
-      </c>
       <c r="C109">
-        <v>-696680575.1565311</v>
+        <v>-1528334032.1934123</v>
       </c>
       <c r="D109">
-        <v>791516543.2819394</v>
-      </c>
-      <c r="F109">
-        <v>758210692.3306383</v>
+        <v>-745541580.8555696</v>
+      </c>
+      <c r="E109">
+        <v>847028776.1635475</v>
       </c>
       <c r="H109">
-        <v>-409799632.0247088</v>
-      </c>
-      <c r="I109">
-        <v>456067624.0579172</v>
+        <v>811387052.1720412</v>
+      </c>
+      <c r="J109">
+        <v>-438540525.44107014</v>
+      </c>
+      <c r="K109">
+        <v>488053477.5076621</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="C110">
-        <v>86622622.83276843</v>
-      </c>
-      <c r="F110">
+      <c r="B110">
+        <v>-869918203.8641498</v>
+      </c>
+      <c r="D110">
+        <v>92697815.13585022</v>
+      </c>
+      <c r="H110">
         <v>0</v>
       </c>
     </row>
@@ -7058,22 +8145,25 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-550623156.0975677</v>
+        <v>-537942258.7431295</v>
       </c>
       <c r="C118">
-        <v>-571187630.0975677</v>
+        <v>-589240568.6213214</v>
       </c>
       <c r="D118">
-        <v>-784500489.0087055</v>
-      </c>
-      <c r="F118">
-        <v>-768635756.2262975</v>
+        <v>-611247311.7431295</v>
+      </c>
+      <c r="E118">
+        <v>-839520657.8367807</v>
       </c>
       <c r="H118">
-        <v>-533424751.38604546</v>
-      </c>
-      <c r="I118">
-        <v>-369144186.88471794</v>
+        <v>-822543267.652204</v>
+      </c>
+      <c r="J118">
+        <v>-570835970.7409496</v>
+      </c>
+      <c r="K118">
+        <v>-395033750.71400744</v>
       </c>
     </row>
     <row r="119">
@@ -7100,11 +8190,11 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H123">
-        <v>124767240.91434476</v>
-      </c>
-      <c r="I123">
-        <v>-124767240.91434476</v>
+      <c r="J123">
+        <v>133517668.42267509</v>
+      </c>
+      <c r="K123">
+        <v>-133517668.42267509</v>
       </c>
     </row>
     <row r="124">
@@ -7117,13 +8207,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>58823128.751948714</v>
+        <v>315626869.55907595</v>
       </c>
       <c r="C125">
-        <v>196651893.7519487</v>
-      </c>
-      <c r="F125">
-        <v>-578691103.1836579</v>
+        <v>62948630.928521484</v>
+      </c>
+      <c r="D125">
+        <v>210443880.55907592</v>
+      </c>
+      <c r="H125">
+        <v>-619277033.5209385</v>
       </c>
     </row>
     <row r="126">
@@ -7136,22 +8229,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>58823128.751948714</v>
+        <v>315626869.55907595</v>
       </c>
       <c r="C127">
-        <v>196651893.7519487</v>
+        <v>62948630.928521484</v>
       </c>
       <c r="D127">
-        <v>-511952412.3774023</v>
-      </c>
-      <c r="F127">
-        <v>-578691103.1836579</v>
+        <v>210443880.55907592</v>
+      </c>
+      <c r="E127">
+        <v>-547857690.3926368</v>
       </c>
       <c r="H127">
-        <v>907118628.3244456</v>
-      </c>
-      <c r="I127">
-        <v>118427694.49052928</v>
+        <v>-619277033.5209385</v>
+      </c>
+      <c r="J127">
+        <v>970738499.5377433</v>
+      </c>
+      <c r="K127">
+        <v>126733504.15678218</v>
       </c>
     </row>
     <row r="128">
@@ -7159,13 +8255,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>252714006.6813855</v>
+        <v>270440601.7298876</v>
       </c>
       <c r="C128">
-        <v>73389268.68138549</v>
-      </c>
-      <c r="F128">
-        <v>1035151476.7567383</v>
+        <v>270437854.54080325</v>
+      </c>
+      <c r="D128">
+        <v>78536352.72988757</v>
+      </c>
+      <c r="H128">
+        <v>1107750805.6440337</v>
       </c>
     </row>
     <row r="129">
@@ -7173,18 +8272,21 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>241270192.82022387</v>
+        <v>537966358.9662168</v>
       </c>
       <c r="C129">
-        <v>252718758.82022387</v>
-      </c>
-      <c r="F129">
-        <v>73389268.68138549</v>
+        <v>258191440.07008207</v>
+      </c>
+      <c r="D129">
+        <v>270442939.9662168</v>
+      </c>
+      <c r="H129">
+        <v>78536352.72988757</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>